--- a/liste_invites.xlsx
+++ b/liste_invites.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invités" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Invités'!$A$1:$C$120</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Invités'!$A$1:$D$139</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,12 +441,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C120"/>
+  <dimension ref="A1:D139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="66" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,1794 +466,2774 @@
           <t>Lien personnalisé</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Message prêt à envoyer</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Elie Mikolo</t>
+          <t>Couple Blaise Mako</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Elie%20Mikolo&amp;table=4</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Blaise%20Mako&amp;table=1</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Couple Blaise Mako (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Blaise%20Mako&amp;table=1)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Cyril India</t>
+          <t>Couple Suprier Pela</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Cyril%20India&amp;table=4</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Suprier%20Pela&amp;table=1</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Couple Suprier Pela (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Suprier%20Pela&amp;table=1)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Jocelain Katola</t>
+          <t>Couple José Kilundu</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Jocelain%20Katola&amp;table=4</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Jos%C3%A9%20Kilundu&amp;table=1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Couple José Kilundu (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Jos%C3%A9%20Kilundu&amp;table=1)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Boni Kitalumbu</t>
+          <t>Couple Dauphin</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Boni%20Kitalumbu&amp;table=4</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Dauphin&amp;table=1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Couple Dauphin (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Dauphin&amp;table=1)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Deo Sakasaka</t>
+          <t>Couple Edo</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Deo%20Sakasaka&amp;table=4</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Edo&amp;table=1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Couple Edo (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Edo&amp;table=1)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Noël Kibala</t>
+          <t>Couple Kas</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=No%C3%ABl%20Kibala&amp;table=4</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Kas&amp;table=2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Couple Kas (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Kas&amp;table=2)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Christian Kumatoka</t>
+          <t>Couple Tonton Langwana</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Christian%20Kumatoka&amp;table=4</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Tonton%20Langwana&amp;table=2</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Couple Tonton Langwana (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Tonton%20Langwana&amp;table=2)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Couple Arma Ndongisila</t>
+          <t>Couple Nelson Metela</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Couple%20Arma%20Ndongisila&amp;table=4</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Nelson%20Metela&amp;table=2</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Couple Nelson Metela (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Nelson%20Metela&amp;table=2)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Moise Kinzanza</t>
+          <t>Couple Luc Kusekana</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Moise%20Kinzanza&amp;table=4</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Luc%20Kusekana&amp;table=2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Couple Luc Kusekana (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Luc%20Kusekana&amp;table=2)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Andrine Kayiba</t>
+          <t>Couple Jean Zikudiafa</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Andrine%20Kayiba&amp;table=4</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Jean%20Zikudiafa&amp;table=2</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Couple Jean Zikudiafa (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Jean%20Zikudiafa&amp;table=2)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Chansard</t>
+          <t>Dario Kimukedi</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Chansard&amp;table=4</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Dario%20Kimukedi&amp;table=3</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Dario Kimukedi (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Dario%20Kimukedi&amp;table=3)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Gedeon Vundji</t>
+          <t>Giyaume Kimukedi</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Gedeon%20Vundji&amp;table=5</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Giyaume%20Kimukedi&amp;table=3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Giyaume Kimukedi (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Giyaume%20Kimukedi&amp;table=3)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Herman Asalakowu</t>
+          <t>Auguy Maswa</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Herman%20Asalakowu&amp;table=5</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Auguy%20Maswa&amp;table=3</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Auguy Maswa (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Auguy%20Maswa&amp;table=3)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Bientôt Kitapindu</t>
+          <t>Couple Tonton Nagagula</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Bient%C3%B4t%20Kitapindu&amp;table=5</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Tonton%20Nagagula&amp;table=3</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Couple Tonton Nagagula (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Tonton%20Nagagula&amp;table=3)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Jael Kitapindu</t>
+          <t>Salomon Nagagula</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Jael%20Kitapindu&amp;table=5</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Salomon%20Nagagula&amp;table=3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Salomon Nagagula (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Salomon%20Nagagula&amp;table=3)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Couple Dorcas Kibongo</t>
+          <t>Couple Dady</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Couple%20Dorcas%20Kibongo&amp;table=5</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Dady&amp;table=3</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Couple Dady (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Dady&amp;table=3)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Maria Kuyana</t>
+          <t>Couple Vx Djo Salongo</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Maria%20Kuyana&amp;table=5</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Vx%20Djo%20Salongo&amp;table=3</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Couple Vx Djo Salongo (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Vx%20Djo%20Salongo&amp;table=3)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Atufengila</t>
+          <t>Elie Mikolo</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Atufengila&amp;table=5</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Elie%20Mikolo&amp;table=4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Elie Mikolo (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Elie%20Mikolo&amp;table=4)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Dethy</t>
+          <t>Cyril India</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Dethy&amp;table=5</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Cyril%20India&amp;table=4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Cyril India (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Cyril%20India&amp;table=4)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Dani</t>
+          <t>Jocelain Katola</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Dani&amp;table=5</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Jocelain%20Katola&amp;table=4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Jocelain Katola (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Jocelain%20Katola&amp;table=4)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Couple Neto Wazeya</t>
+          <t>Boni Kitalumbu</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Couple%20Neto%20Wazeya&amp;table=6</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Boni%20Kitalumbu&amp;table=4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Boni Kitalumbu (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Boni%20Kitalumbu&amp;table=4)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Osée</t>
+          <t>Deo Sakasaka</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Os%C3%A9e&amp;table=6</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Deo%20Sakasaka&amp;table=4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Deo Sakasaka (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Deo%20Sakasaka&amp;table=4)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Mpela</t>
+          <t>Noël Kibala</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Mpela&amp;table=6</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=No%C3%ABl%20Kibala&amp;table=4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Noël Kibala (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=No%C3%ABl%20Kibala&amp;table=4)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Couple Degaul Wazeya</t>
+          <t>Couple Christian Kumatoka</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Couple%20Degaul%20Wazeya&amp;table=6</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Christian%20Kumatoka&amp;table=4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Couple Christian Kumatoka (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Christian%20Kumatoka&amp;table=4)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Couple Doris Wazeya</t>
+          <t>Couple Arma Ndongisila</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Couple%20Doris%20Wazeya&amp;table=6</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Arma%20Ndongisila&amp;table=4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Couple Arma Ndongisila (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Arma%20Ndongisila&amp;table=4)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Couple Dani et Lepetit Wazeya</t>
+          <t>Moise Kinzanza</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Couple%20Dani%20et%20Lepetit%20Wazeya&amp;table=6</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Moise%20Kinzanza&amp;table=4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Moise Kinzanza (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Moise%20Kinzanza&amp;table=4)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Jeune Premier</t>
+          <t>Andrine Kayiba</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Jeune%20Premier&amp;table=6</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Andrine%20Kayiba&amp;table=4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Andrine Kayiba (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Andrine%20Kayiba&amp;table=4)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Directeurs Sadiki</t>
+          <t>Gedeon Vundji</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Directeurs%20Sadiki&amp;table=7</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Gedeon%20Vundji&amp;table=5</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Gedeon Vundji (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Gedeon%20Vundji&amp;table=5)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Prof Tshiula</t>
+          <t>Herman Asalakowu</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Prof%20Tshiula&amp;table=7</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Herman%20Asalakowu&amp;table=5</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Herman Asalakowu (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Herman%20Asalakowu&amp;table=5)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Ir Fabrice couple</t>
+          <t>Bientôt Kitapindu</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ir%20Fabrice%20couple&amp;table=7</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Bient%C3%B4t%20Kitapindu&amp;table=5</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Bientôt Kitapindu (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Bient%C3%B4t%20Kitapindu&amp;table=5)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Ir José</t>
+          <t>Jael Kitapindu</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ir%20Jos%C3%A9&amp;table=7</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Jael%20Kitapindu&amp;table=5</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Jael Kitapindu (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Jael%20Kitapindu&amp;table=5)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Ir Perci couple</t>
+          <t>Couple Dorcas Kwemudi</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ir%20Perci%20couple&amp;table=7</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Dorcas%20Kwemudi&amp;table=5</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Couple Dorcas Kwemudi (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Dorcas%20Kwemudi&amp;table=5)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Archi Christian</t>
+          <t>Maria Kuyana</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Archi%20Christian&amp;table=7</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Maria%20Kuyana&amp;table=5</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Maria Kuyana (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Maria%20Kuyana&amp;table=5)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Archi Jean Paul</t>
+          <t>Atufengila</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Archi%20Jean%20Paul&amp;table=7</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Atufengila&amp;table=5</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Atufengila (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Atufengila&amp;table=5)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Ir Lucien couple</t>
+          <t>Dethy</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ir%20Lucien%20couple&amp;table=7</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Dethy&amp;table=5</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Dethy (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Dethy&amp;table=5)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Ingénieur BKA Ville</t>
+          <t>Dani</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ing%C3%A9nieur%20BKA%20Ville&amp;table=7</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Dani&amp;table=5</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Dani (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Dani&amp;table=5)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Ir Johny couple</t>
+          <t>Chansard</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ir%20Johny%20couple&amp;table=8</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Chansard&amp;table=5</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Chansard (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Chansard&amp;table=5)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Ir Ridy couple</t>
+          <t>Couple Neto Wazeya</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ir%20Ridy%20couple&amp;table=8</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Neto%20Wazeya&amp;table=6</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Couple Neto Wazeya (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Neto%20Wazeya&amp;table=6)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Ir Gentille couple</t>
+          <t>Osée</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ir%20Gentille%20couple&amp;table=8</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Os%C3%A9e&amp;table=6</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Osée (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Os%C3%A9e&amp;table=6)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Ir Manase Bikila Or couple</t>
+          <t>Mpela</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ir%20Manase%20Bikila%20Or%20couple&amp;table=8</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Mpela&amp;table=6</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Mpela (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Mpela&amp;table=6)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Bricil Ntumba BKA couple</t>
+          <t>Couple Degaul Wazeya</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Bricil%20Ntumba%20BKA%20couple&amp;table=8</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Degaul%20Wazeya&amp;table=6</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Couple Degaul Wazeya (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Degaul%20Wazeya&amp;table=6)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Ir Poly</t>
+          <t>Couple Doris Wazeya</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ir%20Poly&amp;table=8</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Doris%20Wazeya&amp;table=6</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Couple Doris Wazeya (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Doris%20Wazeya&amp;table=6)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Ir George</t>
+          <t>Couple Dani et Lepetit Wazeya</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ir%20George&amp;table=8</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Dani%20et%20Lepetit%20Wazeya&amp;table=6</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Couple Dani et Lepetit Wazeya (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Dani%20et%20Lepetit%20Wazeya&amp;table=6)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Henry</t>
+          <t>Jeune Premier</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Henry&amp;table=8</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Jeune%20Premier&amp;table=6</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Jeune Premier (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Jeune%20Premier&amp;table=6)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Ir Horizon couple</t>
+          <t>Directeurs Sadiki</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ir%20Horizon%20couple&amp;table=9</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Directeurs%20Sadiki&amp;table=7</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Directeurs Sadiki (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Directeurs%20Sadiki&amp;table=7)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Ir Juventus couple</t>
+          <t>Prof Tshiula</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ir%20Juventus%20couple&amp;table=9</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Prof%20Tshiula&amp;table=7</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Prof Tshiula (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Prof%20Tshiula&amp;table=7)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Ir Jonathan Or couple</t>
+          <t>Ir Fabrice couple</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ir%20Jonathan%20Or%20couple&amp;table=9</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Fabrice%20couple&amp;table=7</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ir Fabrice couple (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Fabrice%20couple&amp;table=7)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Ir Judith Acgt couple</t>
+          <t>Ir José</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ir%20Judith%20Acgt%20couple&amp;table=9</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Jos%C3%A9&amp;table=7</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ir José (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Jos%C3%A9&amp;table=7)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Ir Naomie Acgt</t>
+          <t>Ir Perci couple</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ir%20Naomie%20Acgt&amp;table=9</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Perci%20couple&amp;table=7</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ir Perci couple (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Perci%20couple&amp;table=7)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Ir Grâce ACGT</t>
+          <t>Archi Christian</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ir%20Gr%C3%A2ce%20ACGT&amp;table=9</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Archi%20Christian&amp;table=7</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Archi Christian (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Archi%20Christian&amp;table=7)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Ir Herman</t>
+          <t>Archi Jean Paul</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ir%20Herman&amp;table=9</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Archi%20Jean%20Paul&amp;table=7</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Archi Jean Paul (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Archi%20Jean%20Paul&amp;table=7)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Ir Amina</t>
+          <t>Ir Lucien couple</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ir%20Amina&amp;table=9</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Lucien%20couple&amp;table=7</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ir Lucien couple (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Lucien%20couple&amp;table=7)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Ir Gaël</t>
+          <t>Ingénieur BKA Ville</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ir%20Ga%C3%ABl&amp;table=9</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ing%C3%A9nieur%20BKA%20Ville&amp;table=7</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ingénieur BKA Ville (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ing%C3%A9nieur%20BKA%20Ville&amp;table=7)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Vane Covec couple</t>
+          <t>Ir Johny couple</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Vane%20Covec%20couple&amp;table=10</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Johny%20couple&amp;table=8</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ir Johny couple (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Johny%20couple&amp;table=8)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Grâce Covec</t>
+          <t>Ir Ridy couple</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Gr%C3%A2ce%20Covec&amp;table=10</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Ridy%20couple&amp;table=8</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ir Ridy couple (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Ridy%20couple&amp;table=8)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Jeans Denis Covec</t>
+          <t>Ir gentille couple</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Jeans%20Denis%20Covec&amp;table=10</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20gentille%20couple&amp;table=8</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ir gentille couple (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20gentille%20couple&amp;table=8)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Li Covec</t>
+          <t>Ir Manase Bikila Or couple</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Li%20Covec&amp;table=10</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Manase%20Bikila%20Or%20couple&amp;table=8</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ir Manase Bikila Or couple (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Manase%20Bikila%20Or%20couple&amp;table=8)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Cong Covec</t>
+          <t>Bricil Ntumba BKA couple</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Cong%20Covec&amp;table=10</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Bricil%20Ntumba%20BKA%20couple&amp;table=8</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Bricil Ntumba BKA couple (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Bricil%20Ntumba%20BKA%20couple&amp;table=8)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Chen Covec</t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Chen%20Covec&amp;table=10</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Henry&amp;table=8</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Henry (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Henry&amp;table=8)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Wula</t>
+          <t>Ir Poly</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Wula&amp;table=10</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Poly&amp;table=8</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ir Poly (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Poly&amp;table=8)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Chen</t>
+          <t>Ir George</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Chen&amp;table=10</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20George&amp;table=8</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ir George (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20George&amp;table=8)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Amigo Covec</t>
+          <t>Ir Horizon couple</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Amigo%20Covec&amp;table=10</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Horizon%20couple&amp;table=9</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ir Horizon couple (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Horizon%20couple&amp;table=9)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Chan Covec</t>
+          <t>Ir Juventus couple</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Chan%20Covec&amp;table=10</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Juventus%20couple&amp;table=9</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ir Juventus couple (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Juventus%20couple&amp;table=9)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Ir Naomie Aziama</t>
+          <t>Ir Jonathan Or couple</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ir%20Naomie%20Aziama&amp;table=11</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Jonathan%20Or%20couple&amp;table=9</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ir Jonathan Or couple (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Jonathan%20Or%20couple&amp;table=9)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Ir Nelly Kapinga</t>
+          <t>Ir Judith Acgt couple</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ir%20Nelly%20Kapinga&amp;table=11</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Judith%20Acgt%20couple&amp;table=9</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ir Judith Acgt couple (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Judith%20Acgt%20couple&amp;table=9)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Ir Carine Pela</t>
+          <t>Ir Naomie Acgt</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ir%20Carine%20Pela&amp;table=11</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Naomie%20Acgt&amp;table=9</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ir Naomie Acgt (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Naomie%20Acgt&amp;table=9)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Ir Sephora Makota</t>
+          <t>Ir Grâce ACGT</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ir%20Sephora%20Makota&amp;table=11</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Gr%C3%A2ce%20ACGT&amp;table=9</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ir Grâce ACGT (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Gr%C3%A2ce%20ACGT&amp;table=9)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Ir Gabriel Tembo</t>
+          <t>Ir Herman</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ir%20Gabriel%20Tembo&amp;table=11</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Herman&amp;table=9</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ir Herman (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Herman&amp;table=9)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Ir Chrispin Kudiakusika</t>
+          <t>Ir Amina</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ir%20Chrispin%20Kudiakusika&amp;table=11</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Amina&amp;table=9</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ir Amina (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Amina&amp;table=9)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Ir Jures Kisombe</t>
+          <t>Ir Gaël</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ir%20Jures%20Kisombe&amp;table=11</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Ga%C3%ABl&amp;table=9</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ir Gaël (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Ga%C3%ABl&amp;table=9)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Ir Didier</t>
+          <t>Me Vane</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ir%20Didier&amp;table=11</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Me%20Vane&amp;table=10</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Me Vane (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Me%20Vane&amp;table=10)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Ir Bervely Totokani</t>
+          <t>Mm Grâce</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ir%20Bervely%20Totokani&amp;table=11</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Mm%20Gr%C3%A2ce&amp;table=10</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Mm Grâce (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Mm%20Gr%C3%A2ce&amp;table=10)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Ir Palice Kumbelu couple</t>
+          <t>Jeans Denis</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ir%20Palice%20Kumbelu%20couple&amp;table=11</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Jeans%20Denis&amp;table=10</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Jeans Denis (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Jeans%20Denis&amp;table=10)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Ir Péguy Mwana Mputu</t>
+          <t>Li Lizheng</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ir%20P%C3%A9guy%20Mwana%20Mputu&amp;table=12</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Li%20Lizheng&amp;table=10</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Li Lizheng (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Li%20Lizheng&amp;table=10)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Ir Ndaya Grâce</t>
+          <t>Cong 巩永利</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ir%20Ndaya%20Gr%C3%A2ce&amp;table=12</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Cong%20%E5%B7%A9%E6%B0%B8%E5%88%A9&amp;table=10</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Cong 巩永利 (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Cong%20%E5%B7%A9%E6%B0%B8%E5%88%A9&amp;table=10)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Ir Tyty Mpets</t>
+          <t>Chen 陈洪展</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ir%20Tyty%20Mpets&amp;table=12</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Chen%20%E9%99%88%E6%B4%AA%E5%B1%95&amp;table=10</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Chen 陈洪展 (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Chen%20%E9%99%88%E6%B4%AA%E5%B1%95&amp;table=10)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Ir Hervé Bakitwala</t>
+          <t>Han Mingdong 韩明东</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ir%20Herv%C3%A9%20Bakitwala&amp;table=12</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Han%20Mingdong%20%E9%9F%A9%E6%98%8E%E4%B8%9C&amp;table=10</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Han Mingdong 韩明东 (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Han%20Mingdong%20%E9%9F%A9%E6%98%8E%E4%B8%9C&amp;table=10)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Ir Gradi Mtshaudi</t>
+          <t>Chan Ami 翁茂术</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ir%20Gradi%20Mtshaudi&amp;table=12</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Chan%20Ami%20%E7%BF%81%E8%8C%82%E6%9C%AF&amp;table=10</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Chan Ami 翁茂术 (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Chan%20Ami%20%E7%BF%81%E8%8C%82%E6%9C%AF&amp;table=10)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Couple Braime</t>
+          <t>Wula 吴乐</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Couple%20Braime&amp;table=12</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Wula%20%E5%90%B4%E4%B9%90&amp;table=10</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Wula 吴乐 (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Wula%20%E5%90%B4%E4%B9%90&amp;table=10)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Ir Trésor Mumeme</t>
+          <t>Chen 池恩</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ir%20Tr%C3%A9sor%20Mumeme&amp;table=12</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Chen%20%E6%B1%A0%E6%81%A9&amp;table=10</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Chen 池恩 (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Chen%20%E6%B1%A0%E6%81%A9&amp;table=10)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Ir Consoler Mwamba</t>
+          <t>Chan 蒋锁</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ir%20Consoler%20Mwamba&amp;table=12</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Chan%20%E8%92%8B%E9%94%81&amp;table=10</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Chan 蒋锁 (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Chan%20%E8%92%8B%E9%94%81&amp;table=10)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Ir Louis Kianza</t>
+          <t>Jong 赵毅乐</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ir%20Louis%20Kianza&amp;table=12</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Jong%20%E8%B5%B5%E6%AF%85%E4%B9%90&amp;table=10</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Jong 赵毅乐 (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Jong%20%E8%B5%B5%E6%AF%85%E4%B9%90&amp;table=10)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Vx Junior</t>
+          <t>Anne 安</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Vx%20Junior&amp;table=13</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Anne%20%E5%AE%89&amp;table=10</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Anne 安 (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Anne%20%E5%AE%89&amp;table=10)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Mm Mitshia</t>
+          <t>Ir Naomie Aziama</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Mm%20Mitshia&amp;table=13</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Naomie%20Aziama&amp;table=11</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ir Naomie Aziama (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Naomie%20Aziama&amp;table=11)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Couple Leon</t>
+          <t>Ir Nelly Kapinga</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Couple%20Leon&amp;table=13</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Nelly%20Kapinga&amp;table=11</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ir Nelly Kapinga (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Nelly%20Kapinga&amp;table=11)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Vieux Jarick</t>
+          <t>Ir Carine Pela</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Vieux%20Jarick&amp;table=13</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Carine%20Pela&amp;table=11</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ir Carine Pela (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Carine%20Pela&amp;table=11)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Couple Dr Héritier</t>
+          <t>Ir Sephora Makota</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Couple%20Dr%20H%C3%A9ritier&amp;table=13</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Sephora%20Makota&amp;table=11</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ir Sephora Makota (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Sephora%20Makota&amp;table=11)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Couple Nené</t>
+          <t>Ir Gabriel Tembo</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Couple%20Nen%C3%A9&amp;table=13</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Gabriel%20Tembo&amp;table=11</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ir Gabriel Tembo (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Gabriel%20Tembo&amp;table=11)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Mm Fifi Salongo</t>
+          <t>Ir Chrispin Kudiakusika</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Mm%20Fifi%20Salongo&amp;table=13</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Chrispin%20Kudiakusika&amp;table=11</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ir Chrispin Kudiakusika (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Chrispin%20Kudiakusika&amp;table=11)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Goza Salongo</t>
+          <t>Ir Jures Kisombe</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Goza%20Salongo&amp;table=13</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Jures%20Kisombe&amp;table=11</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ir Jures Kisombe (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Jures%20Kisombe&amp;table=11)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Ir Edo Naka</t>
+          <t>Ir Didier</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ir%20Edo%20Naka&amp;table=14</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Didier&amp;table=11</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ir Didier (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Didier&amp;table=11)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Ir Carol Mundele</t>
+          <t>Ir Bervely Totokani</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ir%20Carol%20Mundele&amp;table=14</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Bervely%20Totokani&amp;table=11</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ir Bervely Totokani (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Bervely%20Totokani&amp;table=11)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Josue Naka</t>
+          <t>Ir Palice Kumbelu couple</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Josue%20Naka&amp;table=14</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Palice%20Kumbelu%20couple&amp;table=11</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ir Palice Kumbelu couple (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Palice%20Kumbelu%20couple&amp;table=11)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Maxim Makengo</t>
+          <t>Ir Péguy Mwana Mputu</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Maxim%20Makengo&amp;table=14</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20P%C3%A9guy%20Mwana%20Mputu&amp;table=12</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ir Péguy Mwana Mputu (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20P%C3%A9guy%20Mwana%20Mputu&amp;table=12)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Sarah Nakasila</t>
+          <t>Ir Ndaya Grâce</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Sarah%20Nakasila&amp;table=14</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Ndaya%20Gr%C3%A2ce&amp;table=12</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ir Ndaya Grâce (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Ndaya%20Gr%C3%A2ce&amp;table=12)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Reno Mezo</t>
+          <t>Ir Tyty Mpets</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Reno%20Mezo&amp;table=14</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Tyty%20Mpets&amp;table=12</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ir Tyty Mpets (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Tyty%20Mpets&amp;table=12)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Vicky Mezo</t>
+          <t>Ir Hervé Bakitwala</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Vicky%20Mezo&amp;table=14</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Herv%C3%A9%20Bakitwala&amp;table=12</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ir Hervé Bakitwala (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Herv%C3%A9%20Bakitwala&amp;table=12)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Leatitia Nakamula</t>
+          <t>Ir Gradi Mtshaudi</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Leatitia%20Nakamula&amp;table=14</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Gradi%20Mtshaudi&amp;table=12</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ir Gradi Mtshaudi (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Gradi%20Mtshaudi&amp;table=12)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Jenaf Kusanza</t>
+          <t>Couple Braime</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Jenaf%20Kusanza&amp;table=14</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Braime&amp;table=12</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Couple Braime (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Braime&amp;table=12)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Dieu Mindanda</t>
+          <t>Ir Trésor Mumeme</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Dieu%20Mindanda&amp;table=14</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Tr%C3%A9sor%20Mumeme&amp;table=12</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ir Trésor Mumeme (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Tr%C3%A9sor%20Mumeme&amp;table=12)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Esthy Mayele</t>
+          <t>Ir Consoler Mwamba</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Esthy%20Mayele&amp;table=14</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Consoler%20Mwamba&amp;table=12</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ir Consoler Mwamba (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Consoler%20Mwamba&amp;table=12)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Ir Rigo</t>
+          <t>Ruth Matundu</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ir%20Rigo&amp;table=14</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ruth%20Matundu&amp;table=12</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ruth Matundu (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ruth%20Matundu&amp;table=12)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Benie et Exau</t>
+          <t>Ir Louis Kianza</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Benie%20et%20Exau&amp;table=15</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Louis%20Kianza&amp;table=12</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ir Louis Kianza (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Louis%20Kianza&amp;table=12)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Raul Mundele</t>
+          <t>Vx Junior</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Raul%20Mundele&amp;table=15</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Vx%20Junior&amp;table=13</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Vx Junior (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Vx%20Junior&amp;table=13)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Deo et Elsa</t>
+          <t>Mm Mitshia</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Deo%20et%20Elsa&amp;table=15</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Mm%20Mitshia&amp;table=13</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Mm Mitshia (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Mm%20Mitshia&amp;table=13)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Qui et Grace</t>
+          <t>Couple Leon</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Qui%20et%20Grace&amp;table=15</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Leon&amp;table=13</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Couple Leon (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Leon&amp;table=13)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Elohime et Israëlla</t>
+          <t>Vieux Jarick</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Elohime%20et%20Isra%C3%ABlla&amp;table=15</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Vieux%20Jarick&amp;table=13</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Vieux Jarick (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Vieux%20Jarick&amp;table=13)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Deborah Malemba</t>
+          <t>Couple Dr Héritier</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Deborah%20Malemba&amp;table=15</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Dr%20H%C3%A9ritier&amp;table=13</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Couple Dr Héritier (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Dr%20H%C3%A9ritier&amp;table=13)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Oncle Zo couple</t>
+          <t>Couple Nené</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Oncle%20Zo%20couple&amp;table=15</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Nen%C3%A9&amp;table=13</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Couple Nené (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Nen%C3%A9&amp;table=13)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Papa et Maman</t>
+          <t>Mm Fifi Salongo</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Papa%20et%20Maman&amp;table=16</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Mm%20Fifi%20Salongo&amp;table=13</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Mm Fifi Salongo (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Mm%20Fifi%20Salongo&amp;table=13)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Miriam Kuse couple</t>
+          <t>Goza Salongo</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Miriam%20Kuse%20couple&amp;table=16</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Goza%20Salongo&amp;table=13</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Goza Salongo (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Goza%20Salongo&amp;table=13)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Tantine Vicky</t>
+          <t>Ir Edo Naka</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Tantine%20Vicky&amp;table=16</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Edo%20Naka&amp;table=14</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ir Edo Naka (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Edo%20Naka&amp;table=14)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Oncle Kinonde</t>
+          <t>Ir Carol Mundele</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Oncle%20Kinonde&amp;table=16</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Carol%20Mundele&amp;table=14</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ir Carol Mundele (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Carol%20Mundele&amp;table=14)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Gedeon Mutu couple (Mabangu)</t>
+          <t>Josue Naka</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Gedeon%20Mutu%20couple%20%28Mabangu%29&amp;table=16</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Josue%20Naka&amp;table=14</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Josue Naka (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Josue%20Naka&amp;table=14)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Juvenal Kuse</t>
+          <t>Maxim Makengo</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Juvenal%20Kuse&amp;table=16</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Maxim%20Makengo&amp;table=14</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Maxim Makengo (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Maxim%20Makengo&amp;table=14)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Oncle Adolphe</t>
+          <t>Sarah Nakasila</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Oncle%20Adolphe&amp;table=16</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Sarah%20Nakasila&amp;table=14</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Sarah Nakasila (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Sarah%20Nakasila&amp;table=14)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Ma Bienvenue couple</t>
+          <t>Reno Mezo</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Ma%20Bienvenue%20couple&amp;table=16</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Reno%20Mezo&amp;table=14</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Reno Mezo (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Reno%20Mezo&amp;table=14)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Mama</t>
+          <t>Vicky Mezo</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Mama&amp;table=16</t>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Vicky%20Mezo&amp;table=14</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Vicky Mezo (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Vicky%20Mezo&amp;table=14)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Leatitia Nakamula</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Leatitia%20Nakamula&amp;table=14</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Leatitia Nakamula (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Leatitia%20Nakamula&amp;table=14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Jenaf Kusanza</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Jenaf%20Kusanza&amp;table=14</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Jenaf Kusanza (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Jenaf%20Kusanza&amp;table=14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Dieu Mindanda</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Dieu%20Mindanda&amp;table=14</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Dieu Mindanda (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Dieu%20Mindanda&amp;table=14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Esthy Mayele</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Esthy%20Mayele&amp;table=14</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Esthy Mayele (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Esthy%20Mayele&amp;table=14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Ir Rigo</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Rigo&amp;table=14</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ir Rigo (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Rigo&amp;table=14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Benie, Exau et Deo</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Benie%2C%20Exau%20et%20Deo&amp;table=15</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Benie, Exau et Deo (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Benie%2C%20Exau%20et%20Deo&amp;table=15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Elsa et Josepha</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Elsa%20et%20Josepha&amp;table=15</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Elsa et Josepha (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Elsa%20et%20Josepha&amp;table=15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Qui et Grace</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Qui%20et%20Grace&amp;table=15</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Qui et Grace (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Qui%20et%20Grace&amp;table=15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Elohime et Israëlla</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Elohime%20et%20Isra%C3%ABlla&amp;table=15</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Elohime et Israëlla (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Elohime%20et%20Isra%C3%ABlla&amp;table=15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Deborah Malemba</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Deborah%20Malemba&amp;table=15</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Deborah Malemba (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Deborah%20Malemba&amp;table=15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Oncle Zo couple</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Oncle%20Zo%20couple&amp;table=15</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Oncle Zo couple (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Oncle%20Zo%20couple&amp;table=15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="B120" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Papa et Maman</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Papa%20et%20Maman&amp;table=16</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Papa et Maman (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Papa%20et%20Maman&amp;table=16)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Miriam Kuse couple</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Miriam%20Kuse%20couple&amp;table=16</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Miriam Kuse couple (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Miriam%20Kuse%20couple&amp;table=16)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Tantine Vicky</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Tantine%20Vicky&amp;table=16</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Tantine Vicky (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Tantine%20Vicky&amp;table=16)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Gedeon Mutu</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Gedeon%20Mutu&amp;table=16</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Gedeon Mutu (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Gedeon%20Mutu&amp;table=16)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>Mbangu Mutu</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Mbangu%20Mutu&amp;table=16</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Mbangu Mutu (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Mbangu%20Mutu&amp;table=16)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Juvenal Kuse</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Juvenal%20Kuse&amp;table=16</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Juvenal Kuse (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Juvenal%20Kuse&amp;table=16)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>Ma Bienvenue couple</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ma%20Bienvenue%20couple&amp;table=16</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ma Bienvenue couple (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ma%20Bienvenue%20couple&amp;table=16)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Mama</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Mama&amp;table=16</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Mama (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Mama&amp;table=16)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>Kulutu Kumbele</t>
         </is>
       </c>
-      <c r="C120" s="3" t="inlineStr">
-        <is>
-          <t>https://TON-DOMAINE.exemple/invitation.html?invite=Kulutu%20Kumbele&amp;table=16</t>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Kulutu%20Kumbele&amp;table=16</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Kulutu Kumbele (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Kulutu%20Kumbele&amp;table=16)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C120"/>
+  <autoFilter ref="A1:D139"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
@@ -2373,6 +3354,25 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C118" r:id="rId117"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C119" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C139" r:id="rId138"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/liste_invites.xlsx
+++ b/liste_invites.xlsx
@@ -446,8 +446,8 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="66" customWidth="1" min="3" max="3"/>
-    <col width="80" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="84" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -483,12 +483,12 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Blaise%20Mako&amp;table=1</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Blaise%20Mako&amp;table=1</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Couple Blaise Mako (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Blaise%20Mako&amp;table=1)</t>
+          <t>Invitation de Couple Blaise Mako (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Blaise%20Mako&amp;table=1)</t>
         </is>
       </c>
     </row>
@@ -503,12 +503,12 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Suprier%20Pela&amp;table=1</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Suprier%20Pela&amp;table=1</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Couple Suprier Pela (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Suprier%20Pela&amp;table=1)</t>
+          <t>Invitation de Couple Suprier Pela (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Suprier%20Pela&amp;table=1)</t>
         </is>
       </c>
     </row>
@@ -523,12 +523,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Jos%C3%A9%20Kilundu&amp;table=1</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Jos%C3%A9%20Kilundu&amp;table=1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Couple José Kilundu (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Jos%C3%A9%20Kilundu&amp;table=1)</t>
+          <t>Invitation de Couple José Kilundu (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Jos%C3%A9%20Kilundu&amp;table=1)</t>
         </is>
       </c>
     </row>
@@ -543,12 +543,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Dauphin&amp;table=1</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Dauphin&amp;table=1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Couple Dauphin (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Dauphin&amp;table=1)</t>
+          <t>Invitation de Couple Dauphin (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Dauphin&amp;table=1)</t>
         </is>
       </c>
     </row>
@@ -563,12 +563,12 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Edo&amp;table=1</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Edo&amp;table=1</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Couple Edo (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Edo&amp;table=1)</t>
+          <t>Invitation de Couple Edo (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Edo&amp;table=1)</t>
         </is>
       </c>
     </row>
@@ -583,12 +583,12 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Kas&amp;table=2</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Kas&amp;table=2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Couple Kas (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Kas&amp;table=2)</t>
+          <t>Invitation de Couple Kas (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Kas&amp;table=2)</t>
         </is>
       </c>
     </row>
@@ -603,12 +603,12 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Tonton%20Langwana&amp;table=2</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Tonton%20Langwana&amp;table=2</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Couple Tonton Langwana (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Tonton%20Langwana&amp;table=2)</t>
+          <t>Invitation de Couple Tonton Langwana (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Tonton%20Langwana&amp;table=2)</t>
         </is>
       </c>
     </row>
@@ -623,12 +623,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Nelson%20Metela&amp;table=2</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Nelson%20Metela&amp;table=2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Couple Nelson Metela (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Nelson%20Metela&amp;table=2)</t>
+          <t>Invitation de Couple Nelson Metela (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Nelson%20Metela&amp;table=2)</t>
         </is>
       </c>
     </row>
@@ -643,12 +643,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Luc%20Kusekana&amp;table=2</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Luc%20Kusekana&amp;table=2</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Couple Luc Kusekana (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Luc%20Kusekana&amp;table=2)</t>
+          <t>Invitation de Couple Luc Kusekana (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Luc%20Kusekana&amp;table=2)</t>
         </is>
       </c>
     </row>
@@ -663,12 +663,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Jean%20Zikudiafa&amp;table=2</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Jean%20Zikudiafa&amp;table=2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Couple Jean Zikudiafa (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Jean%20Zikudiafa&amp;table=2)</t>
+          <t>Invitation de Couple Jean Zikudiafa (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Jean%20Zikudiafa&amp;table=2)</t>
         </is>
       </c>
     </row>
@@ -683,12 +683,12 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Dario%20Kimukedi&amp;table=3</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Dario%20Kimukedi&amp;table=3</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Dario Kimukedi (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Dario%20Kimukedi&amp;table=3)</t>
+          <t>Invitation de Dario Kimukedi (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Dario%20Kimukedi&amp;table=3)</t>
         </is>
       </c>
     </row>
@@ -703,12 +703,12 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Giyaume%20Kimukedi&amp;table=3</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Giyaume%20Kimukedi&amp;table=3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Giyaume Kimukedi (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Giyaume%20Kimukedi&amp;table=3)</t>
+          <t>Invitation de Giyaume Kimukedi (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Giyaume%20Kimukedi&amp;table=3)</t>
         </is>
       </c>
     </row>
@@ -723,12 +723,12 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Auguy%20Maswa&amp;table=3</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Auguy%20Maswa&amp;table=3</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Auguy Maswa (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Auguy%20Maswa&amp;table=3)</t>
+          <t>Invitation de Auguy Maswa (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Auguy%20Maswa&amp;table=3)</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Tonton%20Nagagula&amp;table=3</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Tonton%20Nagagula&amp;table=3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Couple Tonton Nagagula (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Tonton%20Nagagula&amp;table=3)</t>
+          <t>Invitation de Couple Tonton Nagagula (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Tonton%20Nagagula&amp;table=3)</t>
         </is>
       </c>
     </row>
@@ -763,12 +763,12 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Salomon%20Nagagula&amp;table=3</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Salomon%20Nagagula&amp;table=3</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Salomon Nagagula (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Salomon%20Nagagula&amp;table=3)</t>
+          <t>Invitation de Salomon Nagagula (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Salomon%20Nagagula&amp;table=3)</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Dady&amp;table=3</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Dady&amp;table=3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Couple Dady (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Dady&amp;table=3)</t>
+          <t>Invitation de Couple Dady (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Dady&amp;table=3)</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Vx%20Djo%20Salongo&amp;table=3</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Vx%20Djo%20Salongo&amp;table=3</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Couple Vx Djo Salongo (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Vx%20Djo%20Salongo&amp;table=3)</t>
+          <t>Invitation de Couple Vx Djo Salongo (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Vx%20Djo%20Salongo&amp;table=3)</t>
         </is>
       </c>
     </row>
@@ -823,12 +823,12 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Elie%20Mikolo&amp;table=4</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Elie%20Mikolo&amp;table=4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Elie Mikolo (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Elie%20Mikolo&amp;table=4)</t>
+          <t>Invitation de Elie Mikolo (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Elie%20Mikolo&amp;table=4)</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Cyril%20India&amp;table=4</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Cyril%20India&amp;table=4</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Cyril India (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Cyril%20India&amp;table=4)</t>
+          <t>Invitation de Cyril India (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Cyril%20India&amp;table=4)</t>
         </is>
       </c>
     </row>
@@ -863,12 +863,12 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Jocelain%20Katola&amp;table=4</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Jocelain%20Katola&amp;table=4</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Jocelain Katola (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Jocelain%20Katola&amp;table=4)</t>
+          <t>Invitation de Jocelain Katola (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Jocelain%20Katola&amp;table=4)</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Boni%20Kitalumbu&amp;table=4</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Boni%20Kitalumbu&amp;table=4</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Boni Kitalumbu (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Boni%20Kitalumbu&amp;table=4)</t>
+          <t>Invitation de Boni Kitalumbu (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Boni%20Kitalumbu&amp;table=4)</t>
         </is>
       </c>
     </row>
@@ -903,12 +903,12 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Deo%20Sakasaka&amp;table=4</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Deo%20Sakasaka&amp;table=4</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Deo Sakasaka (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Deo%20Sakasaka&amp;table=4)</t>
+          <t>Invitation de Deo Sakasaka (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Deo%20Sakasaka&amp;table=4)</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=No%C3%ABl%20Kibala&amp;table=4</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=No%C3%ABl%20Kibala&amp;table=4</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Noël Kibala (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=No%C3%ABl%20Kibala&amp;table=4)</t>
+          <t>Invitation de Noël Kibala (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=No%C3%ABl%20Kibala&amp;table=4)</t>
         </is>
       </c>
     </row>
@@ -943,12 +943,12 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Christian%20Kumatoka&amp;table=4</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Christian%20Kumatoka&amp;table=4</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Couple Christian Kumatoka (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Christian%20Kumatoka&amp;table=4)</t>
+          <t>Invitation de Couple Christian Kumatoka (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Christian%20Kumatoka&amp;table=4)</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Arma%20Ndongisila&amp;table=4</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Arma%20Ndongisila&amp;table=4</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Couple Arma Ndongisila (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Arma%20Ndongisila&amp;table=4)</t>
+          <t>Invitation de Couple Arma Ndongisila (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Arma%20Ndongisila&amp;table=4)</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Moise%20Kinzanza&amp;table=4</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Moise%20Kinzanza&amp;table=4</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Moise Kinzanza (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Moise%20Kinzanza&amp;table=4)</t>
+          <t>Invitation de Moise Kinzanza (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Moise%20Kinzanza&amp;table=4)</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Andrine%20Kayiba&amp;table=4</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Andrine%20Kayiba&amp;table=4</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Andrine Kayiba (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Andrine%20Kayiba&amp;table=4)</t>
+          <t>Invitation de Andrine Kayiba (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Andrine%20Kayiba&amp;table=4)</t>
         </is>
       </c>
     </row>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Gedeon%20Vundji&amp;table=5</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Gedeon%20Vundji&amp;table=5</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Gedeon Vundji (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Gedeon%20Vundji&amp;table=5)</t>
+          <t>Invitation de Gedeon Vundji (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Gedeon%20Vundji&amp;table=5)</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Herman%20Asalakowu&amp;table=5</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Herman%20Asalakowu&amp;table=5</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Herman Asalakowu (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Herman%20Asalakowu&amp;table=5)</t>
+          <t>Invitation de Herman Asalakowu (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Herman%20Asalakowu&amp;table=5)</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Bient%C3%B4t%20Kitapindu&amp;table=5</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Bient%C3%B4t%20Kitapindu&amp;table=5</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Bientôt Kitapindu (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Bient%C3%B4t%20Kitapindu&amp;table=5)</t>
+          <t>Invitation de Bientôt Kitapindu (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Bient%C3%B4t%20Kitapindu&amp;table=5)</t>
         </is>
       </c>
     </row>
@@ -1083,12 +1083,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Jael%20Kitapindu&amp;table=5</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Jael%20Kitapindu&amp;table=5</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Jael Kitapindu (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Jael%20Kitapindu&amp;table=5)</t>
+          <t>Invitation de Jael Kitapindu (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Jael%20Kitapindu&amp;table=5)</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Dorcas%20Kwemudi&amp;table=5</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Dorcas%20Kwemudi&amp;table=5</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Couple Dorcas Kwemudi (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Dorcas%20Kwemudi&amp;table=5)</t>
+          <t>Invitation de Couple Dorcas Kwemudi (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Dorcas%20Kwemudi&amp;table=5)</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Maria%20Kuyana&amp;table=5</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Maria%20Kuyana&amp;table=5</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Maria Kuyana (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Maria%20Kuyana&amp;table=5)</t>
+          <t>Invitation de Maria Kuyana (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Maria%20Kuyana&amp;table=5)</t>
         </is>
       </c>
     </row>
@@ -1143,12 +1143,12 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Atufengila&amp;table=5</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Atufengila&amp;table=5</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Atufengila (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Atufengila&amp;table=5)</t>
+          <t>Invitation de Atufengila (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Atufengila&amp;table=5)</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Dethy&amp;table=5</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Dethy&amp;table=5</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Dethy (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Dethy&amp;table=5)</t>
+          <t>Invitation de Dethy (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Dethy&amp;table=5)</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Dani&amp;table=5</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Dani&amp;table=5</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Dani (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Dani&amp;table=5)</t>
+          <t>Invitation de Dani (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Dani&amp;table=5)</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Chansard&amp;table=5</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Chansard&amp;table=5</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Chansard (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Chansard&amp;table=5)</t>
+          <t>Invitation de Chansard (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Chansard&amp;table=5)</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Neto%20Wazeya&amp;table=6</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Neto%20Wazeya&amp;table=6</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Couple Neto Wazeya (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Neto%20Wazeya&amp;table=6)</t>
+          <t>Invitation de Couple Neto Wazeya (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Neto%20Wazeya&amp;table=6)</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Os%C3%A9e&amp;table=6</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Os%C3%A9e&amp;table=6</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Osée (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Os%C3%A9e&amp;table=6)</t>
+          <t>Invitation de Osée (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Os%C3%A9e&amp;table=6)</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Mpela&amp;table=6</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Mpela&amp;table=6</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Mpela (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Mpela&amp;table=6)</t>
+          <t>Invitation de Mpela (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Mpela&amp;table=6)</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1283,12 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Degaul%20Wazeya&amp;table=6</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Degaul%20Wazeya&amp;table=6</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Couple Degaul Wazeya (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Degaul%20Wazeya&amp;table=6)</t>
+          <t>Invitation de Couple Degaul Wazeya (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Degaul%20Wazeya&amp;table=6)</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Doris%20Wazeya&amp;table=6</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Doris%20Wazeya&amp;table=6</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Couple Doris Wazeya (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Doris%20Wazeya&amp;table=6)</t>
+          <t>Invitation de Couple Doris Wazeya (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Doris%20Wazeya&amp;table=6)</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Dani%20et%20Lepetit%20Wazeya&amp;table=6</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Dani%20et%20Lepetit%20Wazeya&amp;table=6</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Couple Dani et Lepetit Wazeya (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Dani%20et%20Lepetit%20Wazeya&amp;table=6)</t>
+          <t>Invitation de Couple Dani et Lepetit Wazeya (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Dani%20et%20Lepetit%20Wazeya&amp;table=6)</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Jeune%20Premier&amp;table=6</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Jeune%20Premier&amp;table=6</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Jeune Premier (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Jeune%20Premier&amp;table=6)</t>
+          <t>Invitation de Jeune Premier (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Jeune%20Premier&amp;table=6)</t>
         </is>
       </c>
     </row>
@@ -1363,12 +1363,12 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Directeurs%20Sadiki&amp;table=7</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Directeurs%20Sadiki&amp;table=7</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Directeurs Sadiki (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Directeurs%20Sadiki&amp;table=7)</t>
+          <t>Invitation de Directeurs Sadiki (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Directeurs%20Sadiki&amp;table=7)</t>
         </is>
       </c>
     </row>
@@ -1383,12 +1383,12 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Prof%20Tshiula&amp;table=7</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Prof%20Tshiula&amp;table=7</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Prof Tshiula (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Prof%20Tshiula&amp;table=7)</t>
+          <t>Invitation de Prof Tshiula (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Prof%20Tshiula&amp;table=7)</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Fabrice%20couple&amp;table=7</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Fabrice%20couple&amp;table=7</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Fabrice couple (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Fabrice%20couple&amp;table=7)</t>
+          <t>Invitation de Ir Fabrice couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Fabrice%20couple&amp;table=7)</t>
         </is>
       </c>
     </row>
@@ -1423,12 +1423,12 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Jos%C3%A9&amp;table=7</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Jos%C3%A9&amp;table=7</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir José (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Jos%C3%A9&amp;table=7)</t>
+          <t>Invitation de Ir José (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Jos%C3%A9&amp;table=7)</t>
         </is>
       </c>
     </row>
@@ -1443,12 +1443,12 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Perci%20couple&amp;table=7</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Perci%20couple&amp;table=7</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Perci couple (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Perci%20couple&amp;table=7)</t>
+          <t>Invitation de Ir Perci couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Perci%20couple&amp;table=7)</t>
         </is>
       </c>
     </row>
@@ -1463,12 +1463,12 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Archi%20Christian&amp;table=7</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Archi%20Christian&amp;table=7</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Archi Christian (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Archi%20Christian&amp;table=7)</t>
+          <t>Invitation de Archi Christian (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Archi%20Christian&amp;table=7)</t>
         </is>
       </c>
     </row>
@@ -1483,12 +1483,12 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Archi%20Jean%20Paul&amp;table=7</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Archi%20Jean%20Paul&amp;table=7</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Archi Jean Paul (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Archi%20Jean%20Paul&amp;table=7)</t>
+          <t>Invitation de Archi Jean Paul (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Archi%20Jean%20Paul&amp;table=7)</t>
         </is>
       </c>
     </row>
@@ -1503,12 +1503,12 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Lucien%20couple&amp;table=7</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Lucien%20couple&amp;table=7</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Lucien couple (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Lucien%20couple&amp;table=7)</t>
+          <t>Invitation de Ir Lucien couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Lucien%20couple&amp;table=7)</t>
         </is>
       </c>
     </row>
@@ -1523,12 +1523,12 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ing%C3%A9nieur%20BKA%20Ville&amp;table=7</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ing%C3%A9nieur%20BKA%20Ville&amp;table=7</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ingénieur BKA Ville (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ing%C3%A9nieur%20BKA%20Ville&amp;table=7)</t>
+          <t>Invitation de Ingénieur BKA Ville (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ing%C3%A9nieur%20BKA%20Ville&amp;table=7)</t>
         </is>
       </c>
     </row>
@@ -1543,12 +1543,12 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Johny%20couple&amp;table=8</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Johny%20couple&amp;table=8</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Johny couple (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Johny%20couple&amp;table=8)</t>
+          <t>Invitation de Ir Johny couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Johny%20couple&amp;table=8)</t>
         </is>
       </c>
     </row>
@@ -1563,12 +1563,12 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Ridy%20couple&amp;table=8</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Ridy%20couple&amp;table=8</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Ridy couple (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Ridy%20couple&amp;table=8)</t>
+          <t>Invitation de Ir Ridy couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Ridy%20couple&amp;table=8)</t>
         </is>
       </c>
     </row>
@@ -1583,12 +1583,12 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20gentille%20couple&amp;table=8</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20gentille%20couple&amp;table=8</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir gentille couple (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20gentille%20couple&amp;table=8)</t>
+          <t>Invitation de Ir gentille couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20gentille%20couple&amp;table=8)</t>
         </is>
       </c>
     </row>
@@ -1603,12 +1603,12 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Manase%20Bikila%20Or%20couple&amp;table=8</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Manase%20Bikila%20Or%20couple&amp;table=8</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Manase Bikila Or couple (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Manase%20Bikila%20Or%20couple&amp;table=8)</t>
+          <t>Invitation de Ir Manase Bikila Or couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Manase%20Bikila%20Or%20couple&amp;table=8)</t>
         </is>
       </c>
     </row>
@@ -1623,12 +1623,12 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Bricil%20Ntumba%20BKA%20couple&amp;table=8</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Bricil%20Ntumba%20BKA%20couple&amp;table=8</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Bricil Ntumba BKA couple (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Bricil%20Ntumba%20BKA%20couple&amp;table=8)</t>
+          <t>Invitation de Bricil Ntumba BKA couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Bricil%20Ntumba%20BKA%20couple&amp;table=8)</t>
         </is>
       </c>
     </row>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Henry&amp;table=8</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Henry&amp;table=8</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Henry (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Henry&amp;table=8)</t>
+          <t>Invitation de Henry (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Henry&amp;table=8)</t>
         </is>
       </c>
     </row>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Poly&amp;table=8</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Poly&amp;table=8</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Poly (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Poly&amp;table=8)</t>
+          <t>Invitation de Ir Poly (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Poly&amp;table=8)</t>
         </is>
       </c>
     </row>
@@ -1683,12 +1683,12 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20George&amp;table=8</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20George&amp;table=8</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir George (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20George&amp;table=8)</t>
+          <t>Invitation de Ir George (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20George&amp;table=8)</t>
         </is>
       </c>
     </row>
@@ -1703,12 +1703,12 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Horizon%20couple&amp;table=9</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Horizon%20couple&amp;table=9</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Horizon couple (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Horizon%20couple&amp;table=9)</t>
+          <t>Invitation de Ir Horizon couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Horizon%20couple&amp;table=9)</t>
         </is>
       </c>
     </row>
@@ -1723,12 +1723,12 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Juventus%20couple&amp;table=9</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Juventus%20couple&amp;table=9</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Juventus couple (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Juventus%20couple&amp;table=9)</t>
+          <t>Invitation de Ir Juventus couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Juventus%20couple&amp;table=9)</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Jonathan%20Or%20couple&amp;table=9</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Jonathan%20Or%20couple&amp;table=9</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Jonathan Or couple (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Jonathan%20Or%20couple&amp;table=9)</t>
+          <t>Invitation de Ir Jonathan Or couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Jonathan%20Or%20couple&amp;table=9)</t>
         </is>
       </c>
     </row>
@@ -1763,12 +1763,12 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Judith%20Acgt%20couple&amp;table=9</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Judith%20Acgt%20couple&amp;table=9</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Judith Acgt couple (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Judith%20Acgt%20couple&amp;table=9)</t>
+          <t>Invitation de Ir Judith Acgt couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Judith%20Acgt%20couple&amp;table=9)</t>
         </is>
       </c>
     </row>
@@ -1783,12 +1783,12 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Naomie%20Acgt&amp;table=9</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Naomie%20Acgt&amp;table=9</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Naomie Acgt (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Naomie%20Acgt&amp;table=9)</t>
+          <t>Invitation de Ir Naomie Acgt (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Naomie%20Acgt&amp;table=9)</t>
         </is>
       </c>
     </row>
@@ -1803,12 +1803,12 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Gr%C3%A2ce%20ACGT&amp;table=9</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Gr%C3%A2ce%20ACGT&amp;table=9</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Grâce ACGT (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Gr%C3%A2ce%20ACGT&amp;table=9)</t>
+          <t>Invitation de Ir Grâce ACGT (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Gr%C3%A2ce%20ACGT&amp;table=9)</t>
         </is>
       </c>
     </row>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Herman&amp;table=9</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Herman&amp;table=9</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Herman (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Herman&amp;table=9)</t>
+          <t>Invitation de Ir Herman (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Herman&amp;table=9)</t>
         </is>
       </c>
     </row>
@@ -1843,12 +1843,12 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Amina&amp;table=9</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Amina&amp;table=9</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Amina (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Amina&amp;table=9)</t>
+          <t>Invitation de Ir Amina (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Amina&amp;table=9)</t>
         </is>
       </c>
     </row>
@@ -1863,12 +1863,12 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Ga%C3%ABl&amp;table=9</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Ga%C3%ABl&amp;table=9</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Gaël (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Ga%C3%ABl&amp;table=9)</t>
+          <t>Invitation de Ir Gaël (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Ga%C3%ABl&amp;table=9)</t>
         </is>
       </c>
     </row>
@@ -1883,12 +1883,12 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Me%20Vane&amp;table=10</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Me%20Vane&amp;table=10</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Me Vane (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Me%20Vane&amp;table=10)</t>
+          <t>Invitation de Me Vane (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Me%20Vane&amp;table=10)</t>
         </is>
       </c>
     </row>
@@ -1903,12 +1903,12 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Mm%20Gr%C3%A2ce&amp;table=10</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Mm%20Gr%C3%A2ce&amp;table=10</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Mm Grâce (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Mm%20Gr%C3%A2ce&amp;table=10)</t>
+          <t>Invitation de Mm Grâce (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Mm%20Gr%C3%A2ce&amp;table=10)</t>
         </is>
       </c>
     </row>
@@ -1923,12 +1923,12 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Jeans%20Denis&amp;table=10</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Jeans%20Denis&amp;table=10</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Jeans Denis (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Jeans%20Denis&amp;table=10)</t>
+          <t>Invitation de Jeans Denis (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Jeans%20Denis&amp;table=10)</t>
         </is>
       </c>
     </row>
@@ -1943,12 +1943,12 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Li%20Lizheng&amp;table=10</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Li%20Lizheng&amp;table=10</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Li Lizheng (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Li%20Lizheng&amp;table=10)</t>
+          <t>Invitation de Li Lizheng (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Li%20Lizheng&amp;table=10)</t>
         </is>
       </c>
     </row>
@@ -1963,12 +1963,12 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Cong%20%E5%B7%A9%E6%B0%B8%E5%88%A9&amp;table=10</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Cong%20%E5%B7%A9%E6%B0%B8%E5%88%A9&amp;table=10</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Cong 巩永利 (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Cong%20%E5%B7%A9%E6%B0%B8%E5%88%A9&amp;table=10)</t>
+          <t>Invitation de Cong 巩永利 (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Cong%20%E5%B7%A9%E6%B0%B8%E5%88%A9&amp;table=10)</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Chen%20%E9%99%88%E6%B4%AA%E5%B1%95&amp;table=10</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Chen%20%E9%99%88%E6%B4%AA%E5%B1%95&amp;table=10</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Chen 陈洪展 (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Chen%20%E9%99%88%E6%B4%AA%E5%B1%95&amp;table=10)</t>
+          <t>Invitation de Chen 陈洪展 (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Chen%20%E9%99%88%E6%B4%AA%E5%B1%95&amp;table=10)</t>
         </is>
       </c>
     </row>
@@ -2003,12 +2003,12 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Han%20Mingdong%20%E9%9F%A9%E6%98%8E%E4%B8%9C&amp;table=10</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Han%20Mingdong%20%E9%9F%A9%E6%98%8E%E4%B8%9C&amp;table=10</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Han Mingdong 韩明东 (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Han%20Mingdong%20%E9%9F%A9%E6%98%8E%E4%B8%9C&amp;table=10)</t>
+          <t>Invitation de Han Mingdong 韩明东 (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Han%20Mingdong%20%E9%9F%A9%E6%98%8E%E4%B8%9C&amp;table=10)</t>
         </is>
       </c>
     </row>
@@ -2023,12 +2023,12 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Chan%20Ami%20%E7%BF%81%E8%8C%82%E6%9C%AF&amp;table=10</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Chan%20Ami%20%E7%BF%81%E8%8C%82%E6%9C%AF&amp;table=10</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Chan Ami 翁茂术 (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Chan%20Ami%20%E7%BF%81%E8%8C%82%E6%9C%AF&amp;table=10)</t>
+          <t>Invitation de Chan Ami 翁茂术 (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Chan%20Ami%20%E7%BF%81%E8%8C%82%E6%9C%AF&amp;table=10)</t>
         </is>
       </c>
     </row>
@@ -2043,12 +2043,12 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Wula%20%E5%90%B4%E4%B9%90&amp;table=10</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Wula%20%E5%90%B4%E4%B9%90&amp;table=10</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Wula 吴乐 (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Wula%20%E5%90%B4%E4%B9%90&amp;table=10)</t>
+          <t>Invitation de Wula 吴乐 (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Wula%20%E5%90%B4%E4%B9%90&amp;table=10)</t>
         </is>
       </c>
     </row>
@@ -2063,12 +2063,12 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Chen%20%E6%B1%A0%E6%81%A9&amp;table=10</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Chen%20%E6%B1%A0%E6%81%A9&amp;table=10</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Chen 池恩 (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Chen%20%E6%B1%A0%E6%81%A9&amp;table=10)</t>
+          <t>Invitation de Chen 池恩 (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Chen%20%E6%B1%A0%E6%81%A9&amp;table=10)</t>
         </is>
       </c>
     </row>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Chan%20%E8%92%8B%E9%94%81&amp;table=10</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Chan%20%E8%92%8B%E9%94%81&amp;table=10</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Chan 蒋锁 (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Chan%20%E8%92%8B%E9%94%81&amp;table=10)</t>
+          <t>Invitation de Chan 蒋锁 (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Chan%20%E8%92%8B%E9%94%81&amp;table=10)</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Jong%20%E8%B5%B5%E6%AF%85%E4%B9%90&amp;table=10</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Jong%20%E8%B5%B5%E6%AF%85%E4%B9%90&amp;table=10</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Jong 赵毅乐 (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Jong%20%E8%B5%B5%E6%AF%85%E4%B9%90&amp;table=10)</t>
+          <t>Invitation de Jong 赵毅乐 (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Jong%20%E8%B5%B5%E6%AF%85%E4%B9%90&amp;table=10)</t>
         </is>
       </c>
     </row>
@@ -2123,12 +2123,12 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Anne%20%E5%AE%89&amp;table=10</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Anne%20%E5%AE%89&amp;table=10</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Anne 安 (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Anne%20%E5%AE%89&amp;table=10)</t>
+          <t>Invitation de Anne 安 (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Anne%20%E5%AE%89&amp;table=10)</t>
         </is>
       </c>
     </row>
@@ -2143,12 +2143,12 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Naomie%20Aziama&amp;table=11</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Naomie%20Aziama&amp;table=11</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Naomie Aziama (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Naomie%20Aziama&amp;table=11)</t>
+          <t>Invitation de Ir Naomie Aziama (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Naomie%20Aziama&amp;table=11)</t>
         </is>
       </c>
     </row>
@@ -2163,12 +2163,12 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Nelly%20Kapinga&amp;table=11</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Nelly%20Kapinga&amp;table=11</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Nelly Kapinga (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Nelly%20Kapinga&amp;table=11)</t>
+          <t>Invitation de Ir Nelly Kapinga (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Nelly%20Kapinga&amp;table=11)</t>
         </is>
       </c>
     </row>
@@ -2183,12 +2183,12 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Carine%20Pela&amp;table=11</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Carine%20Pela&amp;table=11</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Carine Pela (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Carine%20Pela&amp;table=11)</t>
+          <t>Invitation de Ir Carine Pela (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Carine%20Pela&amp;table=11)</t>
         </is>
       </c>
     </row>
@@ -2203,12 +2203,12 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Sephora%20Makota&amp;table=11</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Sephora%20Makota&amp;table=11</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Sephora Makota (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Sephora%20Makota&amp;table=11)</t>
+          <t>Invitation de Ir Sephora Makota (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Sephora%20Makota&amp;table=11)</t>
         </is>
       </c>
     </row>
@@ -2223,12 +2223,12 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Gabriel%20Tembo&amp;table=11</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Gabriel%20Tembo&amp;table=11</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Gabriel Tembo (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Gabriel%20Tembo&amp;table=11)</t>
+          <t>Invitation de Ir Gabriel Tembo (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Gabriel%20Tembo&amp;table=11)</t>
         </is>
       </c>
     </row>
@@ -2243,12 +2243,12 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Chrispin%20Kudiakusika&amp;table=11</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Chrispin%20Kudiakusika&amp;table=11</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Chrispin Kudiakusika (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Chrispin%20Kudiakusika&amp;table=11)</t>
+          <t>Invitation de Ir Chrispin Kudiakusika (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Chrispin%20Kudiakusika&amp;table=11)</t>
         </is>
       </c>
     </row>
@@ -2263,12 +2263,12 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Jures%20Kisombe&amp;table=11</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Jures%20Kisombe&amp;table=11</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Jures Kisombe (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Jures%20Kisombe&amp;table=11)</t>
+          <t>Invitation de Ir Jures Kisombe (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Jures%20Kisombe&amp;table=11)</t>
         </is>
       </c>
     </row>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Didier&amp;table=11</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Didier&amp;table=11</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Didier (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Didier&amp;table=11)</t>
+          <t>Invitation de Ir Didier (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Didier&amp;table=11)</t>
         </is>
       </c>
     </row>
@@ -2303,12 +2303,12 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Bervely%20Totokani&amp;table=11</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Bervely%20Totokani&amp;table=11</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Bervely Totokani (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Bervely%20Totokani&amp;table=11)</t>
+          <t>Invitation de Ir Bervely Totokani (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Bervely%20Totokani&amp;table=11)</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Palice%20Kumbelu%20couple&amp;table=11</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Palice%20Kumbelu%20couple&amp;table=11</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Palice Kumbelu couple (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Palice%20Kumbelu%20couple&amp;table=11)</t>
+          <t>Invitation de Ir Palice Kumbelu couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Palice%20Kumbelu%20couple&amp;table=11)</t>
         </is>
       </c>
     </row>
@@ -2343,12 +2343,12 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20P%C3%A9guy%20Mwana%20Mputu&amp;table=12</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20P%C3%A9guy%20Mwana%20Mputu&amp;table=12</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Péguy Mwana Mputu (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20P%C3%A9guy%20Mwana%20Mputu&amp;table=12)</t>
+          <t>Invitation de Ir Péguy Mwana Mputu (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20P%C3%A9guy%20Mwana%20Mputu&amp;table=12)</t>
         </is>
       </c>
     </row>
@@ -2363,12 +2363,12 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Ndaya%20Gr%C3%A2ce&amp;table=12</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Ndaya%20Gr%C3%A2ce&amp;table=12</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Ndaya Grâce (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Ndaya%20Gr%C3%A2ce&amp;table=12)</t>
+          <t>Invitation de Ir Ndaya Grâce (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Ndaya%20Gr%C3%A2ce&amp;table=12)</t>
         </is>
       </c>
     </row>
@@ -2383,12 +2383,12 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Tyty%20Mpets&amp;table=12</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Tyty%20Mpets&amp;table=12</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Tyty Mpets (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Tyty%20Mpets&amp;table=12)</t>
+          <t>Invitation de Ir Tyty Mpets (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Tyty%20Mpets&amp;table=12)</t>
         </is>
       </c>
     </row>
@@ -2403,12 +2403,12 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Herv%C3%A9%20Bakitwala&amp;table=12</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Herv%C3%A9%20Bakitwala&amp;table=12</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Hervé Bakitwala (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Herv%C3%A9%20Bakitwala&amp;table=12)</t>
+          <t>Invitation de Ir Hervé Bakitwala (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Herv%C3%A9%20Bakitwala&amp;table=12)</t>
         </is>
       </c>
     </row>
@@ -2423,12 +2423,12 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Gradi%20Mtshaudi&amp;table=12</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Gradi%20Mtshaudi&amp;table=12</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Gradi Mtshaudi (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Gradi%20Mtshaudi&amp;table=12)</t>
+          <t>Invitation de Ir Gradi Mtshaudi (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Gradi%20Mtshaudi&amp;table=12)</t>
         </is>
       </c>
     </row>
@@ -2443,12 +2443,12 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Braime&amp;table=12</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Braime&amp;table=12</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Couple Braime (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Braime&amp;table=12)</t>
+          <t>Invitation de Couple Braime (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Braime&amp;table=12)</t>
         </is>
       </c>
     </row>
@@ -2463,12 +2463,12 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Tr%C3%A9sor%20Mumeme&amp;table=12</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Tr%C3%A9sor%20Mumeme&amp;table=12</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Trésor Mumeme (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Tr%C3%A9sor%20Mumeme&amp;table=12)</t>
+          <t>Invitation de Ir Trésor Mumeme (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Tr%C3%A9sor%20Mumeme&amp;table=12)</t>
         </is>
       </c>
     </row>
@@ -2483,12 +2483,12 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Consoler%20Mwamba&amp;table=12</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Consoler%20Mwamba&amp;table=12</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Consoler Mwamba (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Consoler%20Mwamba&amp;table=12)</t>
+          <t>Invitation de Ir Consoler Mwamba (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Consoler%20Mwamba&amp;table=12)</t>
         </is>
       </c>
     </row>
@@ -2503,12 +2503,12 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ruth%20Matundu&amp;table=12</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ruth%20Matundu&amp;table=12</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ruth Matundu (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ruth%20Matundu&amp;table=12)</t>
+          <t>Invitation de Ruth Matundu (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ruth%20Matundu&amp;table=12)</t>
         </is>
       </c>
     </row>
@@ -2523,12 +2523,12 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Louis%20Kianza&amp;table=12</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Louis%20Kianza&amp;table=12</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Louis Kianza (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Louis%20Kianza&amp;table=12)</t>
+          <t>Invitation de Ir Louis Kianza (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Louis%20Kianza&amp;table=12)</t>
         </is>
       </c>
     </row>
@@ -2543,12 +2543,12 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Vx%20Junior&amp;table=13</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Vx%20Junior&amp;table=13</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Vx Junior (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Vx%20Junior&amp;table=13)</t>
+          <t>Invitation de Vx Junior (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Vx%20Junior&amp;table=13)</t>
         </is>
       </c>
     </row>
@@ -2563,12 +2563,12 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Mm%20Mitshia&amp;table=13</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Mm%20Mitshia&amp;table=13</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Mm Mitshia (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Mm%20Mitshia&amp;table=13)</t>
+          <t>Invitation de Mm Mitshia (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Mm%20Mitshia&amp;table=13)</t>
         </is>
       </c>
     </row>
@@ -2583,12 +2583,12 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Leon&amp;table=13</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Leon&amp;table=13</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Couple Leon (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Leon&amp;table=13)</t>
+          <t>Invitation de Couple Leon (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Leon&amp;table=13)</t>
         </is>
       </c>
     </row>
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Vieux%20Jarick&amp;table=13</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Vieux%20Jarick&amp;table=13</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Vieux Jarick (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Vieux%20Jarick&amp;table=13)</t>
+          <t>Invitation de Vieux Jarick (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Vieux%20Jarick&amp;table=13)</t>
         </is>
       </c>
     </row>
@@ -2623,12 +2623,12 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Dr%20H%C3%A9ritier&amp;table=13</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Dr%20H%C3%A9ritier&amp;table=13</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Couple Dr Héritier (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Dr%20H%C3%A9ritier&amp;table=13)</t>
+          <t>Invitation de Couple Dr Héritier (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Dr%20H%C3%A9ritier&amp;table=13)</t>
         </is>
       </c>
     </row>
@@ -2643,12 +2643,12 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Nen%C3%A9&amp;table=13</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Nen%C3%A9&amp;table=13</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Couple Nené (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Nen%C3%A9&amp;table=13)</t>
+          <t>Invitation de Couple Nené (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Nen%C3%A9&amp;table=13)</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Mm%20Fifi%20Salongo&amp;table=13</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Mm%20Fifi%20Salongo&amp;table=13</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Mm Fifi Salongo (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Mm%20Fifi%20Salongo&amp;table=13)</t>
+          <t>Invitation de Mm Fifi Salongo (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Mm%20Fifi%20Salongo&amp;table=13)</t>
         </is>
       </c>
     </row>
@@ -2683,12 +2683,12 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Goza%20Salongo&amp;table=13</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Goza%20Salongo&amp;table=13</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Goza Salongo (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Goza%20Salongo&amp;table=13)</t>
+          <t>Invitation de Goza Salongo (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Goza%20Salongo&amp;table=13)</t>
         </is>
       </c>
     </row>
@@ -2703,12 +2703,12 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Edo%20Naka&amp;table=14</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Edo%20Naka&amp;table=14</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Edo Naka (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Edo%20Naka&amp;table=14)</t>
+          <t>Invitation de Ir Edo Naka (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Edo%20Naka&amp;table=14)</t>
         </is>
       </c>
     </row>
@@ -2723,12 +2723,12 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Carol%20Mundele&amp;table=14</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Carol%20Mundele&amp;table=14</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Carol Mundele (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Carol%20Mundele&amp;table=14)</t>
+          <t>Invitation de Ir Carol Mundele (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Carol%20Mundele&amp;table=14)</t>
         </is>
       </c>
     </row>
@@ -2743,12 +2743,12 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Josue%20Naka&amp;table=14</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Josue%20Naka&amp;table=14</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Josue Naka (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Josue%20Naka&amp;table=14)</t>
+          <t>Invitation de Josue Naka (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Josue%20Naka&amp;table=14)</t>
         </is>
       </c>
     </row>
@@ -2763,12 +2763,12 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Maxim%20Makengo&amp;table=14</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Maxim%20Makengo&amp;table=14</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Maxim Makengo (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Maxim%20Makengo&amp;table=14)</t>
+          <t>Invitation de Maxim Makengo (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Maxim%20Makengo&amp;table=14)</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Sarah%20Nakasila&amp;table=14</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Sarah%20Nakasila&amp;table=14</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Sarah Nakasila (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Sarah%20Nakasila&amp;table=14)</t>
+          <t>Invitation de Sarah Nakasila (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Sarah%20Nakasila&amp;table=14)</t>
         </is>
       </c>
     </row>
@@ -2803,12 +2803,12 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Reno%20Mezo&amp;table=14</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Reno%20Mezo&amp;table=14</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Reno Mezo (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Reno%20Mezo&amp;table=14)</t>
+          <t>Invitation de Reno Mezo (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Reno%20Mezo&amp;table=14)</t>
         </is>
       </c>
     </row>
@@ -2823,12 +2823,12 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Vicky%20Mezo&amp;table=14</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Vicky%20Mezo&amp;table=14</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Vicky Mezo (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Vicky%20Mezo&amp;table=14)</t>
+          <t>Invitation de Vicky Mezo (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Vicky%20Mezo&amp;table=14)</t>
         </is>
       </c>
     </row>
@@ -2843,12 +2843,12 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Leatitia%20Nakamula&amp;table=14</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Leatitia%20Nakamula&amp;table=14</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Leatitia Nakamula (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Leatitia%20Nakamula&amp;table=14)</t>
+          <t>Invitation de Leatitia Nakamula (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Leatitia%20Nakamula&amp;table=14)</t>
         </is>
       </c>
     </row>
@@ -2863,12 +2863,12 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Jenaf%20Kusanza&amp;table=14</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Jenaf%20Kusanza&amp;table=14</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Jenaf Kusanza (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Jenaf%20Kusanza&amp;table=14)</t>
+          <t>Invitation de Jenaf Kusanza (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Jenaf%20Kusanza&amp;table=14)</t>
         </is>
       </c>
     </row>
@@ -2883,12 +2883,12 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Dieu%20Mindanda&amp;table=14</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Dieu%20Mindanda&amp;table=14</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Dieu Mindanda (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Dieu%20Mindanda&amp;table=14)</t>
+          <t>Invitation de Dieu Mindanda (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Dieu%20Mindanda&amp;table=14)</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Esthy%20Mayele&amp;table=14</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Esthy%20Mayele&amp;table=14</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Esthy Mayele (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Esthy%20Mayele&amp;table=14)</t>
+          <t>Invitation de Esthy Mayele (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Esthy%20Mayele&amp;table=14)</t>
         </is>
       </c>
     </row>
@@ -2923,12 +2923,12 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Rigo&amp;table=14</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Rigo&amp;table=14</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Rigo (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Rigo&amp;table=14)</t>
+          <t>Invitation de Ir Rigo (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Rigo&amp;table=14)</t>
         </is>
       </c>
     </row>
@@ -2943,12 +2943,12 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Benie%2C%20Exau%20et%20Deo&amp;table=15</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Benie%2C%20Exau%20et%20Deo&amp;table=15</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Benie, Exau et Deo (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Benie%2C%20Exau%20et%20Deo&amp;table=15)</t>
+          <t>Invitation de Benie, Exau et Deo (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Benie%2C%20Exau%20et%20Deo&amp;table=15)</t>
         </is>
       </c>
     </row>
@@ -2963,12 +2963,12 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Elsa%20et%20Josepha&amp;table=15</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Elsa%20et%20Josepha&amp;table=15</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Elsa et Josepha (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Elsa%20et%20Josepha&amp;table=15)</t>
+          <t>Invitation de Elsa et Josepha (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Elsa%20et%20Josepha&amp;table=15)</t>
         </is>
       </c>
     </row>
@@ -2983,12 +2983,12 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Qui%20et%20Grace&amp;table=15</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Qui%20et%20Grace&amp;table=15</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Qui et Grace (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Qui%20et%20Grace&amp;table=15)</t>
+          <t>Invitation de Qui et Grace (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Qui%20et%20Grace&amp;table=15)</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Elohime%20et%20Isra%C3%ABlla&amp;table=15</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Elohime%20et%20Isra%C3%ABlla&amp;table=15</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Elohime et Israëlla (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Elohime%20et%20Isra%C3%ABlla&amp;table=15)</t>
+          <t>Invitation de Elohime et Israëlla (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Elohime%20et%20Isra%C3%ABlla&amp;table=15)</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Deborah%20Malemba&amp;table=15</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Deborah%20Malemba&amp;table=15</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Deborah Malemba (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Deborah%20Malemba&amp;table=15)</t>
+          <t>Invitation de Deborah Malemba (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Deborah%20Malemba&amp;table=15)</t>
         </is>
       </c>
     </row>
@@ -3043,12 +3043,12 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Oncle%20Zo%20couple&amp;table=15</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Oncle%20Zo%20couple&amp;table=15</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Oncle Zo couple (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Oncle%20Zo%20couple&amp;table=15)</t>
+          <t>Invitation de Oncle Zo couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Oncle%20Zo%20couple&amp;table=15)</t>
         </is>
       </c>
     </row>
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Papa%20et%20Maman&amp;table=16</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Papa%20et%20Maman&amp;table=16</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Papa et Maman (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Papa%20et%20Maman&amp;table=16)</t>
+          <t>Invitation de Papa et Maman (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Papa%20et%20Maman&amp;table=16)</t>
         </is>
       </c>
     </row>
@@ -3083,12 +3083,12 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Miriam%20Kuse%20couple&amp;table=16</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Miriam%20Kuse%20couple&amp;table=16</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Miriam Kuse couple (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Miriam%20Kuse%20couple&amp;table=16)</t>
+          <t>Invitation de Miriam Kuse couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Miriam%20Kuse%20couple&amp;table=16)</t>
         </is>
       </c>
     </row>
@@ -3103,12 +3103,12 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Tantine%20Vicky&amp;table=16</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Tantine%20Vicky&amp;table=16</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Tantine Vicky (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Tantine%20Vicky&amp;table=16)</t>
+          <t>Invitation de Tantine Vicky (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Tantine%20Vicky&amp;table=16)</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Gedeon%20Mutu&amp;table=16</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Gedeon%20Mutu&amp;table=16</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Gedeon Mutu (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Gedeon%20Mutu&amp;table=16)</t>
+          <t>Invitation de Gedeon Mutu (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Gedeon%20Mutu&amp;table=16)</t>
         </is>
       </c>
     </row>
@@ -3143,12 +3143,12 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Mbangu%20Mutu&amp;table=16</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Mbangu%20Mutu&amp;table=16</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Mbangu Mutu (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Mbangu%20Mutu&amp;table=16)</t>
+          <t>Invitation de Mbangu Mutu (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Mbangu%20Mutu&amp;table=16)</t>
         </is>
       </c>
     </row>
@@ -3163,12 +3163,12 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Juvenal%20Kuse&amp;table=16</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Juvenal%20Kuse&amp;table=16</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Juvenal Kuse (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Juvenal%20Kuse&amp;table=16)</t>
+          <t>Invitation de Juvenal Kuse (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Juvenal%20Kuse&amp;table=16)</t>
         </is>
       </c>
     </row>
@@ -3183,12 +3183,12 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ma%20Bienvenue%20couple&amp;table=16</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ma%20Bienvenue%20couple&amp;table=16</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ma Bienvenue couple (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Ma%20Bienvenue%20couple&amp;table=16)</t>
+          <t>Invitation de Ma Bienvenue couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ma%20Bienvenue%20couple&amp;table=16)</t>
         </is>
       </c>
     </row>
@@ -3203,12 +3203,12 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Mama&amp;table=16</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Mama&amp;table=16</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Mama (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Mama&amp;table=16)</t>
+          <t>Invitation de Mama (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Mama&amp;table=16)</t>
         </is>
       </c>
     </row>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Kulutu%20Kumbele&amp;table=16</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Kulutu%20Kumbele&amp;table=16</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Kulutu Kumbele (https://edonak.github.io/invitation-tresor-merveille/invitation.html?invite=Kulutu%20Kumbele&amp;table=16)</t>
+          <t>Invitation de Kulutu Kumbele (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Kulutu%20Kumbele&amp;table=16)</t>
         </is>
       </c>
     </row>

--- a/liste_invites.xlsx
+++ b/liste_invites.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invités" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Invités'!$A$1:$D$139</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Invités'!$A$1:$D$141</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,13 +441,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D139"/>
+  <dimension ref="A1:D141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="84" customWidth="1" min="4" max="4"/>
+    <col width="76" customWidth="1" min="3" max="3"/>
+    <col width="90" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1214,21 +1214,21 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Couple Neto Wazeya</t>
+          <t>Mokou Joyce</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Neto%20Wazeya&amp;table=6</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Mokou%20Joyce&amp;table=5</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Couple Neto Wazeya (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Neto%20Wazeya&amp;table=6)</t>
+          <t>Invitation de Mokou Joyce (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Mokou%20Joyce&amp;table=5)</t>
         </is>
       </c>
     </row>
@@ -1238,17 +1238,17 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Osée</t>
+          <t>Couple Neto Wazeya</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Os%C3%A9e&amp;table=6</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Neto%20Wazeya&amp;table=6</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Osée (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Os%C3%A9e&amp;table=6)</t>
+          <t>Invitation de Couple Neto Wazeya (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Neto%20Wazeya&amp;table=6)</t>
         </is>
       </c>
     </row>
@@ -1258,17 +1258,17 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Mpela</t>
+          <t>Osée</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Mpela&amp;table=6</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Os%C3%A9e&amp;table=6</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Mpela (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Mpela&amp;table=6)</t>
+          <t>Invitation de Osée (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Os%C3%A9e&amp;table=6)</t>
         </is>
       </c>
     </row>
@@ -1278,17 +1278,17 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Couple Degaul Wazeya</t>
+          <t>Mpela</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Degaul%20Wazeya&amp;table=6</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Mpela&amp;table=6</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Couple Degaul Wazeya (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Degaul%20Wazeya&amp;table=6)</t>
+          <t>Invitation de Mpela (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Mpela&amp;table=6)</t>
         </is>
       </c>
     </row>
@@ -1298,17 +1298,17 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Couple Doris Wazeya</t>
+          <t>Couple Degaul Wazeya</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Doris%20Wazeya&amp;table=6</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Degaul%20Wazeya&amp;table=6</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Couple Doris Wazeya (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Doris%20Wazeya&amp;table=6)</t>
+          <t>Invitation de Couple Degaul Wazeya (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Degaul%20Wazeya&amp;table=6)</t>
         </is>
       </c>
     </row>
@@ -1318,17 +1318,17 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Couple Dani et Lepetit Wazeya</t>
+          <t>Couple Doris Wazeya</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Dani%20et%20Lepetit%20Wazeya&amp;table=6</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Doris%20Wazeya&amp;table=6</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Couple Dani et Lepetit Wazeya (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Dani%20et%20Lepetit%20Wazeya&amp;table=6)</t>
+          <t>Invitation de Couple Doris Wazeya (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Doris%20Wazeya&amp;table=6)</t>
         </is>
       </c>
     </row>
@@ -1338,37 +1338,37 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Jeune Premier</t>
+          <t>Couple Dani et Lepetit Wazeya</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Jeune%20Premier&amp;table=6</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Dani%20et%20Lepetit%20Wazeya&amp;table=6</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Jeune Premier (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Jeune%20Premier&amp;table=6)</t>
+          <t>Invitation de Couple Dani et Lepetit Wazeya (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Dani%20et%20Lepetit%20Wazeya&amp;table=6)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Directeurs Sadiki</t>
+          <t>Jeune Premier</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Directeurs%20Sadiki&amp;table=7</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Jeune%20Premier&amp;table=6</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Directeurs Sadiki (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Directeurs%20Sadiki&amp;table=7)</t>
+          <t>Invitation de Jeune Premier (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Jeune%20Premier&amp;table=6)</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Prof Tshiula</t>
+          <t>Directeurs Sadiki</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Prof%20Tshiula&amp;table=7</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Directeurs%20Sadiki&amp;table=7</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Prof Tshiula (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Prof%20Tshiula&amp;table=7)</t>
+          <t>Invitation de Directeurs Sadiki (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Directeurs%20Sadiki&amp;table=7)</t>
         </is>
       </c>
     </row>
@@ -1398,17 +1398,17 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Ir Fabrice couple</t>
+          <t>Prof Tshiula</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Fabrice%20couple&amp;table=7</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Prof%20Tshiula&amp;table=7</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Fabrice couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Fabrice%20couple&amp;table=7)</t>
+          <t>Invitation de Prof Tshiula (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Prof%20Tshiula&amp;table=7)</t>
         </is>
       </c>
     </row>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Ir José</t>
+          <t>Ir Fabrice couple</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Jos%C3%A9&amp;table=7</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Fabrice%20couple&amp;table=7</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir José (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Jos%C3%A9&amp;table=7)</t>
+          <t>Invitation de Ir Fabrice couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Fabrice%20couple&amp;table=7)</t>
         </is>
       </c>
     </row>
@@ -1438,17 +1438,17 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Ir Perci couple</t>
+          <t>Ir José</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Perci%20couple&amp;table=7</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Jos%C3%A9&amp;table=7</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Perci couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Perci%20couple&amp;table=7)</t>
+          <t>Invitation de Ir José (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Jos%C3%A9&amp;table=7)</t>
         </is>
       </c>
     </row>
@@ -1458,17 +1458,17 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Archi Christian</t>
+          <t>Ir Perci couple</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Archi%20Christian&amp;table=7</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Perci%20couple&amp;table=7</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Archi Christian (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Archi%20Christian&amp;table=7)</t>
+          <t>Invitation de Ir Perci couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Perci%20couple&amp;table=7)</t>
         </is>
       </c>
     </row>
@@ -1478,17 +1478,17 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Archi Jean Paul</t>
+          <t>Archi Christian</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Archi%20Jean%20Paul&amp;table=7</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Archi%20Christian&amp;table=7</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Archi Jean Paul (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Archi%20Jean%20Paul&amp;table=7)</t>
+          <t>Invitation de Archi Christian (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Archi%20Christian&amp;table=7)</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Ir Lucien couple</t>
+          <t>Archi Jean Paul</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Lucien%20couple&amp;table=7</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Archi%20Jean%20Paul&amp;table=7</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Lucien couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Lucien%20couple&amp;table=7)</t>
+          <t>Invitation de Archi Jean Paul (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Archi%20Jean%20Paul&amp;table=7)</t>
         </is>
       </c>
     </row>
@@ -1518,37 +1518,37 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Ingénieur BKA Ville</t>
+          <t>Ir Lucien couple</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ing%C3%A9nieur%20BKA%20Ville&amp;table=7</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Lucien%20couple&amp;table=7</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ingénieur BKA Ville (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ing%C3%A9nieur%20BKA%20Ville&amp;table=7)</t>
+          <t>Invitation de Ir Lucien couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Lucien%20couple&amp;table=7)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Ir Johny couple</t>
+          <t>Ingénieur BKA Ville</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Johny%20couple&amp;table=8</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ing%C3%A9nieur%20BKA%20Ville&amp;table=7</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Johny couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Johny%20couple&amp;table=8)</t>
+          <t>Invitation de Ingénieur BKA Ville (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ing%C3%A9nieur%20BKA%20Ville&amp;table=7)</t>
         </is>
       </c>
     </row>
@@ -1558,17 +1558,17 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Ir Ridy couple</t>
+          <t>Ir Johny couple</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Ridy%20couple&amp;table=8</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Johny%20couple&amp;table=8</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Ridy couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Ridy%20couple&amp;table=8)</t>
+          <t>Invitation de Ir Johny couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Johny%20couple&amp;table=8)</t>
         </is>
       </c>
     </row>
@@ -1578,17 +1578,17 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Ir gentille couple</t>
+          <t>Ir Ridy couple</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20gentille%20couple&amp;table=8</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Ridy%20couple&amp;table=8</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir gentille couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20gentille%20couple&amp;table=8)</t>
+          <t>Invitation de Ir Ridy couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Ridy%20couple&amp;table=8)</t>
         </is>
       </c>
     </row>
@@ -1598,17 +1598,17 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Ir Manase Bikila Or couple</t>
+          <t>Ir gentille couple</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Manase%20Bikila%20Or%20couple&amp;table=8</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20gentille%20couple&amp;table=8</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Manase Bikila Or couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Manase%20Bikila%20Or%20couple&amp;table=8)</t>
+          <t>Invitation de Ir gentille couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20gentille%20couple&amp;table=8)</t>
         </is>
       </c>
     </row>
@@ -1618,17 +1618,17 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Bricil Ntumba BKA couple</t>
+          <t>Ir Manase Bikila Or couple</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Bricil%20Ntumba%20BKA%20couple&amp;table=8</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Manase%20Bikila%20Or%20couple&amp;table=8</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Bricil Ntumba BKA couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Bricil%20Ntumba%20BKA%20couple&amp;table=8)</t>
+          <t>Invitation de Ir Manase Bikila Or couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Manase%20Bikila%20Or%20couple&amp;table=8)</t>
         </is>
       </c>
     </row>
@@ -1638,17 +1638,17 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Henry</t>
+          <t>Bricil Ntumba BKA couple</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Henry&amp;table=8</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Bricil%20Ntumba%20BKA%20couple&amp;table=8</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Henry (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Henry&amp;table=8)</t>
+          <t>Invitation de Bricil Ntumba BKA couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Bricil%20Ntumba%20BKA%20couple&amp;table=8)</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Ir Poly</t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Poly&amp;table=8</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Henry&amp;table=8</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Poly (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Poly&amp;table=8)</t>
+          <t>Invitation de Henry (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Henry&amp;table=8)</t>
         </is>
       </c>
     </row>
@@ -1678,37 +1678,37 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Ir George</t>
+          <t>Ir Poly</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20George&amp;table=8</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Poly&amp;table=8</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir George (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20George&amp;table=8)</t>
+          <t>Invitation de Ir Poly (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Poly&amp;table=8)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Ir Horizon couple</t>
+          <t>Ir George</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Horizon%20couple&amp;table=9</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20George&amp;table=8</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Horizon couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Horizon%20couple&amp;table=9)</t>
+          <t>Invitation de Ir George (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20George&amp;table=8)</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Ir Juventus couple</t>
+          <t>Ir Horizon couple</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Juventus%20couple&amp;table=9</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Horizon%20couple&amp;table=9</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Juventus couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Juventus%20couple&amp;table=9)</t>
+          <t>Invitation de Ir Horizon couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Horizon%20couple&amp;table=9)</t>
         </is>
       </c>
     </row>
@@ -1738,17 +1738,17 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Ir Jonathan Or couple</t>
+          <t>Ir Juventus couple</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Jonathan%20Or%20couple&amp;table=9</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Juventus%20couple&amp;table=9</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Jonathan Or couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Jonathan%20Or%20couple&amp;table=9)</t>
+          <t>Invitation de Ir Juventus couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Juventus%20couple&amp;table=9)</t>
         </is>
       </c>
     </row>
@@ -1758,17 +1758,17 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Ir Judith Acgt couple</t>
+          <t>Ir Jonathan Or couple</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Judith%20Acgt%20couple&amp;table=9</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Jonathan%20Or%20couple&amp;table=9</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Judith Acgt couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Judith%20Acgt%20couple&amp;table=9)</t>
+          <t>Invitation de Ir Jonathan Or couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Jonathan%20Or%20couple&amp;table=9)</t>
         </is>
       </c>
     </row>
@@ -1778,17 +1778,17 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Ir Naomie Acgt</t>
+          <t>Ir Judith Acgt couple</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Naomie%20Acgt&amp;table=9</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Judith%20Acgt%20couple&amp;table=9</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Naomie Acgt (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Naomie%20Acgt&amp;table=9)</t>
+          <t>Invitation de Ir Judith Acgt couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Judith%20Acgt%20couple&amp;table=9)</t>
         </is>
       </c>
     </row>
@@ -1798,17 +1798,17 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Ir Grâce ACGT</t>
+          <t>Ir Naomie Acgt</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Gr%C3%A2ce%20ACGT&amp;table=9</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Naomie%20Acgt&amp;table=9</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Grâce ACGT (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Gr%C3%A2ce%20ACGT&amp;table=9)</t>
+          <t>Invitation de Ir Naomie Acgt (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Naomie%20Acgt&amp;table=9)</t>
         </is>
       </c>
     </row>
@@ -1818,17 +1818,17 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Ir Herman</t>
+          <t>Ir Grâce ACGT</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Herman&amp;table=9</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Gr%C3%A2ce%20ACGT&amp;table=9</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Herman (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Herman&amp;table=9)</t>
+          <t>Invitation de Ir Grâce ACGT (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Gr%C3%A2ce%20ACGT&amp;table=9)</t>
         </is>
       </c>
     </row>
@@ -1838,17 +1838,17 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Ir Amina</t>
+          <t>Ir Herman</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Amina&amp;table=9</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Herman&amp;table=9</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Amina (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Amina&amp;table=9)</t>
+          <t>Invitation de Ir Herman (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Herman&amp;table=9)</t>
         </is>
       </c>
     </row>
@@ -1858,37 +1858,37 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Ir Gaël</t>
+          <t>Ir Amina</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Ga%C3%ABl&amp;table=9</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Amina&amp;table=9</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Gaël (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Ga%C3%ABl&amp;table=9)</t>
+          <t>Invitation de Ir Amina (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Amina&amp;table=9)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Me Vane</t>
+          <t>Ir Gaël</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Me%20Vane&amp;table=10</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Ga%C3%ABl&amp;table=9</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Me Vane (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Me%20Vane&amp;table=10)</t>
+          <t>Invitation de Ir Gaël (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Ga%C3%ABl&amp;table=9)</t>
         </is>
       </c>
     </row>
@@ -1898,17 +1898,17 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Mm Grâce</t>
+          <t>Me Vane</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Mm%20Gr%C3%A2ce&amp;table=10</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Me%20Vane&amp;table=10</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Mm Grâce (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Mm%20Gr%C3%A2ce&amp;table=10)</t>
+          <t>Invitation de Me Vane (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Me%20Vane&amp;table=10)</t>
         </is>
       </c>
     </row>
@@ -1918,17 +1918,17 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Jeans Denis</t>
+          <t>Mm Grâce</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Jeans%20Denis&amp;table=10</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Mm%20Gr%C3%A2ce&amp;table=10</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Jeans Denis (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Jeans%20Denis&amp;table=10)</t>
+          <t>Invitation de Mm Grâce (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Mm%20Gr%C3%A2ce&amp;table=10)</t>
         </is>
       </c>
     </row>
@@ -1938,17 +1938,17 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Li Lizheng</t>
+          <t>Jeans Denis</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Li%20Lizheng&amp;table=10</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Jeans%20Denis&amp;table=10</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Li Lizheng (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Li%20Lizheng&amp;table=10)</t>
+          <t>Invitation de Jeans Denis (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Jeans%20Denis&amp;table=10)</t>
         </is>
       </c>
     </row>
@@ -1958,17 +1958,17 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Cong 巩永利</t>
+          <t>Li Lizheng</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Cong%20%E5%B7%A9%E6%B0%B8%E5%88%A9&amp;table=10</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Li%20Lizheng&amp;table=10</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Cong 巩永利 (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Cong%20%E5%B7%A9%E6%B0%B8%E5%88%A9&amp;table=10)</t>
+          <t>Invitation de Li Lizheng (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Li%20Lizheng&amp;table=10)</t>
         </is>
       </c>
     </row>
@@ -1978,17 +1978,17 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Chen 陈洪展</t>
+          <t>Cong 巩永利</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Chen%20%E9%99%88%E6%B4%AA%E5%B1%95&amp;table=10</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Cong%20%E5%B7%A9%E6%B0%B8%E5%88%A9&amp;table=10&amp;lang=zh</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Chen 陈洪展 (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Chen%20%E9%99%88%E6%B4%AA%E5%B1%95&amp;table=10)</t>
+          <t>Invitation de Cong 巩永利 (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Cong%20%E5%B7%A9%E6%B0%B8%E5%88%A9&amp;table=10&amp;lang=zh)</t>
         </is>
       </c>
     </row>
@@ -1998,17 +1998,17 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Han Mingdong 韩明东</t>
+          <t>Chen 陈洪展</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Han%20Mingdong%20%E9%9F%A9%E6%98%8E%E4%B8%9C&amp;table=10</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Chen%20%E9%99%88%E6%B4%AA%E5%B1%95&amp;table=10&amp;lang=zh</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Han Mingdong 韩明东 (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Han%20Mingdong%20%E9%9F%A9%E6%98%8E%E4%B8%9C&amp;table=10)</t>
+          <t>Invitation de Chen 陈洪展 (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Chen%20%E9%99%88%E6%B4%AA%E5%B1%95&amp;table=10&amp;lang=zh)</t>
         </is>
       </c>
     </row>
@@ -2018,17 +2018,17 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Chan Ami 翁茂术</t>
+          <t>Han Mingdong 韩明东</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Chan%20Ami%20%E7%BF%81%E8%8C%82%E6%9C%AF&amp;table=10</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Han%20Mingdong%20%E9%9F%A9%E6%98%8E%E4%B8%9C&amp;table=10&amp;lang=zh</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Chan Ami 翁茂术 (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Chan%20Ami%20%E7%BF%81%E8%8C%82%E6%9C%AF&amp;table=10)</t>
+          <t>Invitation de Han Mingdong 韩明东 (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Han%20Mingdong%20%E9%9F%A9%E6%98%8E%E4%B8%9C&amp;table=10&amp;lang=zh)</t>
         </is>
       </c>
     </row>
@@ -2038,17 +2038,17 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Wula 吴乐</t>
+          <t>Chan Ami 翁茂术</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Wula%20%E5%90%B4%E4%B9%90&amp;table=10</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Chan%20Ami%20%E7%BF%81%E8%8C%82%E6%9C%AF&amp;table=10&amp;lang=zh</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Wula 吴乐 (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Wula%20%E5%90%B4%E4%B9%90&amp;table=10)</t>
+          <t>Invitation de Chan Ami 翁茂术 (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Chan%20Ami%20%E7%BF%81%E8%8C%82%E6%9C%AF&amp;table=10&amp;lang=zh)</t>
         </is>
       </c>
     </row>
@@ -2058,17 +2058,17 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Chen 池恩</t>
+          <t>Wula 吴乐</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Chen%20%E6%B1%A0%E6%81%A9&amp;table=10</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Wula%20%E5%90%B4%E4%B9%90&amp;table=10&amp;lang=zh</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Chen 池恩 (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Chen%20%E6%B1%A0%E6%81%A9&amp;table=10)</t>
+          <t>Invitation de Wula 吴乐 (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Wula%20%E5%90%B4%E4%B9%90&amp;table=10&amp;lang=zh)</t>
         </is>
       </c>
     </row>
@@ -2078,17 +2078,17 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Chan 蒋锁</t>
+          <t>Chen 池恩</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Chan%20%E8%92%8B%E9%94%81&amp;table=10</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Chen%20%E6%B1%A0%E6%81%A9&amp;table=10&amp;lang=zh</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Chan 蒋锁 (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Chan%20%E8%92%8B%E9%94%81&amp;table=10)</t>
+          <t>Invitation de Chen 池恩 (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Chen%20%E6%B1%A0%E6%81%A9&amp;table=10&amp;lang=zh)</t>
         </is>
       </c>
     </row>
@@ -2098,17 +2098,17 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Jong 赵毅乐</t>
+          <t>Chan 蒋锁</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Jong%20%E8%B5%B5%E6%AF%85%E4%B9%90&amp;table=10</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Chan%20%E8%92%8B%E9%94%81&amp;table=10&amp;lang=zh</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Jong 赵毅乐 (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Jong%20%E8%B5%B5%E6%AF%85%E4%B9%90&amp;table=10)</t>
+          <t>Invitation de Chan 蒋锁 (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Chan%20%E8%92%8B%E9%94%81&amp;table=10&amp;lang=zh)</t>
         </is>
       </c>
     </row>
@@ -2118,37 +2118,37 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Anne 安</t>
+          <t>Jong 赵毅乐</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Anne%20%E5%AE%89&amp;table=10</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Jong%20%E8%B5%B5%E6%AF%85%E4%B9%90&amp;table=10&amp;lang=zh</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Anne 安 (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Anne%20%E5%AE%89&amp;table=10)</t>
+          <t>Invitation de Jong 赵毅乐 (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Jong%20%E8%B5%B5%E6%AF%85%E4%B9%90&amp;table=10&amp;lang=zh)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Ir Naomie Aziama</t>
+          <t>Anne 安</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Naomie%20Aziama&amp;table=11</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Anne%20%E5%AE%89&amp;table=10&amp;lang=zh</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Naomie Aziama (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Naomie%20Aziama&amp;table=11)</t>
+          <t>Invitation de Anne 安 (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Anne%20%E5%AE%89&amp;table=10&amp;lang=zh)</t>
         </is>
       </c>
     </row>
@@ -2158,17 +2158,17 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Ir Nelly Kapinga</t>
+          <t>Ir Naomie Aziama</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Nelly%20Kapinga&amp;table=11</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Naomie%20Aziama&amp;table=11</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Nelly Kapinga (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Nelly%20Kapinga&amp;table=11)</t>
+          <t>Invitation de Ir Naomie Aziama (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Naomie%20Aziama&amp;table=11)</t>
         </is>
       </c>
     </row>
@@ -2178,17 +2178,17 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Ir Carine Pela</t>
+          <t>Ir Nelly Kapinga</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Carine%20Pela&amp;table=11</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Nelly%20Kapinga&amp;table=11</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Carine Pela (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Carine%20Pela&amp;table=11)</t>
+          <t>Invitation de Ir Nelly Kapinga (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Nelly%20Kapinga&amp;table=11)</t>
         </is>
       </c>
     </row>
@@ -2198,17 +2198,17 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Ir Sephora Makota</t>
+          <t>Ir Carine Pela</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Sephora%20Makota&amp;table=11</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Carine%20Pela&amp;table=11</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Sephora Makota (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Sephora%20Makota&amp;table=11)</t>
+          <t>Invitation de Ir Carine Pela (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Carine%20Pela&amp;table=11)</t>
         </is>
       </c>
     </row>
@@ -2218,17 +2218,17 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Ir Gabriel Tembo</t>
+          <t>Ir Sephora Makota</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Gabriel%20Tembo&amp;table=11</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Sephora%20Makota&amp;table=11</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Gabriel Tembo (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Gabriel%20Tembo&amp;table=11)</t>
+          <t>Invitation de Ir Sephora Makota (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Sephora%20Makota&amp;table=11)</t>
         </is>
       </c>
     </row>
@@ -2238,17 +2238,17 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Ir Chrispin Kudiakusika</t>
+          <t>Ir Gabriel Tembo</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Chrispin%20Kudiakusika&amp;table=11</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Gabriel%20Tembo&amp;table=11</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Chrispin Kudiakusika (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Chrispin%20Kudiakusika&amp;table=11)</t>
+          <t>Invitation de Ir Gabriel Tembo (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Gabriel%20Tembo&amp;table=11)</t>
         </is>
       </c>
     </row>
@@ -2258,17 +2258,17 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Ir Jures Kisombe</t>
+          <t>Ir Chrispin Kudiakusika</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Jures%20Kisombe&amp;table=11</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Chrispin%20Kudiakusika&amp;table=11</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Jures Kisombe (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Jures%20Kisombe&amp;table=11)</t>
+          <t>Invitation de Ir Chrispin Kudiakusika (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Chrispin%20Kudiakusika&amp;table=11)</t>
         </is>
       </c>
     </row>
@@ -2278,17 +2278,17 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Ir Didier</t>
+          <t>Ir Jures Kisombe</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Didier&amp;table=11</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Jures%20Kisombe&amp;table=11</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Didier (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Didier&amp;table=11)</t>
+          <t>Invitation de Ir Jures Kisombe (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Jures%20Kisombe&amp;table=11)</t>
         </is>
       </c>
     </row>
@@ -2298,17 +2298,17 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Ir Bervely Totokani</t>
+          <t>Ir Didier</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Bervely%20Totokani&amp;table=11</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Didier&amp;table=11</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Bervely Totokani (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Bervely%20Totokani&amp;table=11)</t>
+          <t>Invitation de Ir Didier (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Didier&amp;table=11)</t>
         </is>
       </c>
     </row>
@@ -2318,37 +2318,37 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Ir Palice Kumbelu couple</t>
+          <t>Ir Bervely Totokani</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Palice%20Kumbelu%20couple&amp;table=11</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Bervely%20Totokani&amp;table=11</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Palice Kumbelu couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Palice%20Kumbelu%20couple&amp;table=11)</t>
+          <t>Invitation de Ir Bervely Totokani (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Bervely%20Totokani&amp;table=11)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Ir Péguy Mwana Mputu</t>
+          <t>Ir Palice Kumbelu couple</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20P%C3%A9guy%20Mwana%20Mputu&amp;table=12</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Palice%20Kumbelu%20couple&amp;table=11</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Péguy Mwana Mputu (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20P%C3%A9guy%20Mwana%20Mputu&amp;table=12)</t>
+          <t>Invitation de Ir Palice Kumbelu couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Palice%20Kumbelu%20couple&amp;table=11)</t>
         </is>
       </c>
     </row>
@@ -2358,17 +2358,17 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Ir Ndaya Grâce</t>
+          <t>Ir Péguy Mwana Mputu</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Ndaya%20Gr%C3%A2ce&amp;table=12</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20P%C3%A9guy%20Mwana%20Mputu&amp;table=12</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Ndaya Grâce (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Ndaya%20Gr%C3%A2ce&amp;table=12)</t>
+          <t>Invitation de Ir Péguy Mwana Mputu (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20P%C3%A9guy%20Mwana%20Mputu&amp;table=12)</t>
         </is>
       </c>
     </row>
@@ -2378,17 +2378,17 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Ir Tyty Mpets</t>
+          <t>Ir Ndaya Grâce</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Tyty%20Mpets&amp;table=12</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Ndaya%20Gr%C3%A2ce&amp;table=12</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Tyty Mpets (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Tyty%20Mpets&amp;table=12)</t>
+          <t>Invitation de Ir Ndaya Grâce (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Ndaya%20Gr%C3%A2ce&amp;table=12)</t>
         </is>
       </c>
     </row>
@@ -2398,17 +2398,17 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Ir Hervé Bakitwala</t>
+          <t>Ir Tyty Mpets</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Herv%C3%A9%20Bakitwala&amp;table=12</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Tyty%20Mpets&amp;table=12</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Hervé Bakitwala (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Herv%C3%A9%20Bakitwala&amp;table=12)</t>
+          <t>Invitation de Ir Tyty Mpets (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Tyty%20Mpets&amp;table=12)</t>
         </is>
       </c>
     </row>
@@ -2418,17 +2418,17 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Ir Gradi Mtshaudi</t>
+          <t>Ir Hervé Bakitwala</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Gradi%20Mtshaudi&amp;table=12</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Herv%C3%A9%20Bakitwala&amp;table=12</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Gradi Mtshaudi (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Gradi%20Mtshaudi&amp;table=12)</t>
+          <t>Invitation de Ir Hervé Bakitwala (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Herv%C3%A9%20Bakitwala&amp;table=12)</t>
         </is>
       </c>
     </row>
@@ -2438,17 +2438,17 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Couple Braime</t>
+          <t>Ir Gradi Mtshaudi</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Braime&amp;table=12</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Gradi%20Mtshaudi&amp;table=12</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Couple Braime (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Braime&amp;table=12)</t>
+          <t>Invitation de Ir Gradi Mtshaudi (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Gradi%20Mtshaudi&amp;table=12)</t>
         </is>
       </c>
     </row>
@@ -2458,17 +2458,17 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Ir Trésor Mumeme</t>
+          <t>Couple Braime</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Tr%C3%A9sor%20Mumeme&amp;table=12</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Braime&amp;table=12</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Trésor Mumeme (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Tr%C3%A9sor%20Mumeme&amp;table=12)</t>
+          <t>Invitation de Couple Braime (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Braime&amp;table=12)</t>
         </is>
       </c>
     </row>
@@ -2478,17 +2478,17 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Ir Consoler Mwamba</t>
+          <t>Ir Trésor Mumeme</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Consoler%20Mwamba&amp;table=12</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Tr%C3%A9sor%20Mumeme&amp;table=12</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Consoler Mwamba (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Consoler%20Mwamba&amp;table=12)</t>
+          <t>Invitation de Ir Trésor Mumeme (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Tr%C3%A9sor%20Mumeme&amp;table=12)</t>
         </is>
       </c>
     </row>
@@ -2498,17 +2498,17 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Ruth Matundu</t>
+          <t>Ir Consoler Mwamba</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ruth%20Matundu&amp;table=12</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Consoler%20Mwamba&amp;table=12</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ruth Matundu (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ruth%20Matundu&amp;table=12)</t>
+          <t>Invitation de Ir Consoler Mwamba (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Consoler%20Mwamba&amp;table=12)</t>
         </is>
       </c>
     </row>
@@ -2518,57 +2518,57 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Ir Louis Kianza</t>
+          <t>Ruth Matundu</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Louis%20Kianza&amp;table=12</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ruth%20Matundu&amp;table=12</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Louis Kianza (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Louis%20Kianza&amp;table=12)</t>
+          <t>Invitation de Ruth Matundu (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ruth%20Matundu&amp;table=12)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Vx Junior</t>
+          <t>Ir Louis Kianza</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Vx%20Junior&amp;table=13</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Louis%20Kianza&amp;table=12</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Vx Junior (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Vx%20Junior&amp;table=13)</t>
+          <t>Invitation de Ir Louis Kianza (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Louis%20Kianza&amp;table=12)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Mm Mitshia</t>
+          <t>Danilo Nzimbu</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Mm%20Mitshia&amp;table=13</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Danilo%20Nzimbu&amp;table=12</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Mm Mitshia (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Mm%20Mitshia&amp;table=13)</t>
+          <t>Invitation de Danilo Nzimbu (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Danilo%20Nzimbu&amp;table=12)</t>
         </is>
       </c>
     </row>
@@ -2578,17 +2578,17 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Couple Leon</t>
+          <t>Vx Junior</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Leon&amp;table=13</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Vx%20Junior&amp;table=13</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Couple Leon (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Leon&amp;table=13)</t>
+          <t>Invitation de Vx Junior (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Vx%20Junior&amp;table=13)</t>
         </is>
       </c>
     </row>
@@ -2598,17 +2598,17 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Vieux Jarick</t>
+          <t>Mm Mitshia</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Vieux%20Jarick&amp;table=13</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Mm%20Mitshia&amp;table=13</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Vieux Jarick (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Vieux%20Jarick&amp;table=13)</t>
+          <t>Invitation de Mm Mitshia (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Mm%20Mitshia&amp;table=13)</t>
         </is>
       </c>
     </row>
@@ -2618,17 +2618,17 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Couple Dr Héritier</t>
+          <t>Couple Leon</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Dr%20H%C3%A9ritier&amp;table=13</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Leon&amp;table=13</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Couple Dr Héritier (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Dr%20H%C3%A9ritier&amp;table=13)</t>
+          <t>Invitation de Couple Leon (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Leon&amp;table=13)</t>
         </is>
       </c>
     </row>
@@ -2638,17 +2638,17 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Couple Nené</t>
+          <t>Vieux Jarick</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Nen%C3%A9&amp;table=13</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Vieux%20Jarick&amp;table=13</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Couple Nené (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Nen%C3%A9&amp;table=13)</t>
+          <t>Invitation de Vieux Jarick (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Vieux%20Jarick&amp;table=13)</t>
         </is>
       </c>
     </row>
@@ -2658,17 +2658,17 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Mm Fifi Salongo</t>
+          <t>Couple Dr Héritier</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Mm%20Fifi%20Salongo&amp;table=13</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Dr%20H%C3%A9ritier&amp;table=13</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Mm Fifi Salongo (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Mm%20Fifi%20Salongo&amp;table=13)</t>
+          <t>Invitation de Couple Dr Héritier (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Dr%20H%C3%A9ritier&amp;table=13)</t>
         </is>
       </c>
     </row>
@@ -2678,57 +2678,57 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Goza Salongo</t>
+          <t>Couple Nené</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Goza%20Salongo&amp;table=13</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Nen%C3%A9&amp;table=13</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Goza Salongo (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Goza%20Salongo&amp;table=13)</t>
+          <t>Invitation de Couple Nené (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Nen%C3%A9&amp;table=13)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Ir Edo Naka</t>
+          <t>Mm Fifi Salongo</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Edo%20Naka&amp;table=14</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Mm%20Fifi%20Salongo&amp;table=13</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Edo Naka (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Edo%20Naka&amp;table=14)</t>
+          <t>Invitation de Mm Fifi Salongo (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Mm%20Fifi%20Salongo&amp;table=13)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Ir Carol Mundele</t>
+          <t>Goza Salongo</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Carol%20Mundele&amp;table=14</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Goza%20Salongo&amp;table=13</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Carol Mundele (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Carol%20Mundele&amp;table=14)</t>
+          <t>Invitation de Goza Salongo (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Goza%20Salongo&amp;table=13)</t>
         </is>
       </c>
     </row>
@@ -2738,17 +2738,17 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Josue Naka</t>
+          <t>Ir Edo Naka</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Josue%20Naka&amp;table=14</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Edo%20Naka&amp;table=14</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Josue Naka (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Josue%20Naka&amp;table=14)</t>
+          <t>Invitation de Ir Edo Naka (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Edo%20Naka&amp;table=14)</t>
         </is>
       </c>
     </row>
@@ -2758,17 +2758,17 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Maxim Makengo</t>
+          <t>Ir Carol Mundele</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Maxim%20Makengo&amp;table=14</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Carol%20Mundele&amp;table=14</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Maxim Makengo (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Maxim%20Makengo&amp;table=14)</t>
+          <t>Invitation de Ir Carol Mundele (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Carol%20Mundele&amp;table=14)</t>
         </is>
       </c>
     </row>
@@ -2778,17 +2778,17 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Sarah Nakasila</t>
+          <t>Josue Naka</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Sarah%20Nakasila&amp;table=14</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Josue%20Naka&amp;table=14</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Sarah Nakasila (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Sarah%20Nakasila&amp;table=14)</t>
+          <t>Invitation de Josue Naka (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Josue%20Naka&amp;table=14)</t>
         </is>
       </c>
     </row>
@@ -2798,17 +2798,17 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Reno Mezo</t>
+          <t>Maxim Makengo</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Reno%20Mezo&amp;table=14</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Maxim%20Makengo&amp;table=14</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Reno Mezo (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Reno%20Mezo&amp;table=14)</t>
+          <t>Invitation de Maxim Makengo (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Maxim%20Makengo&amp;table=14)</t>
         </is>
       </c>
     </row>
@@ -2818,17 +2818,17 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Vicky Mezo</t>
+          <t>Sarah Nakasila</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Vicky%20Mezo&amp;table=14</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Sarah%20Nakasila&amp;table=14</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Vicky Mezo (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Vicky%20Mezo&amp;table=14)</t>
+          <t>Invitation de Sarah Nakasila (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Sarah%20Nakasila&amp;table=14)</t>
         </is>
       </c>
     </row>
@@ -2838,17 +2838,17 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Leatitia Nakamula</t>
+          <t>Reno Mezo</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Leatitia%20Nakamula&amp;table=14</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Reno%20Mezo&amp;table=14</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Leatitia Nakamula (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Leatitia%20Nakamula&amp;table=14)</t>
+          <t>Invitation de Reno Mezo (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Reno%20Mezo&amp;table=14)</t>
         </is>
       </c>
     </row>
@@ -2858,17 +2858,17 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Jenaf Kusanza</t>
+          <t>Vicky Mezo</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Jenaf%20Kusanza&amp;table=14</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Vicky%20Mezo&amp;table=14</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Jenaf Kusanza (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Jenaf%20Kusanza&amp;table=14)</t>
+          <t>Invitation de Vicky Mezo (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Vicky%20Mezo&amp;table=14)</t>
         </is>
       </c>
     </row>
@@ -2878,17 +2878,17 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Dieu Mindanda</t>
+          <t>Leatitia Nakamula</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Dieu%20Mindanda&amp;table=14</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Leatitia%20Nakamula&amp;table=14</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Dieu Mindanda (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Dieu%20Mindanda&amp;table=14)</t>
+          <t>Invitation de Leatitia Nakamula (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Leatitia%20Nakamula&amp;table=14)</t>
         </is>
       </c>
     </row>
@@ -2898,17 +2898,17 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Esthy Mayele</t>
+          <t>Jenaf Kusanza</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Esthy%20Mayele&amp;table=14</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Jenaf%20Kusanza&amp;table=14</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Esthy Mayele (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Esthy%20Mayele&amp;table=14)</t>
+          <t>Invitation de Jenaf Kusanza (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Jenaf%20Kusanza&amp;table=14)</t>
         </is>
       </c>
     </row>
@@ -2918,57 +2918,57 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Ir Rigo</t>
+          <t>Dieu Mindanda</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Rigo&amp;table=14</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Dieu%20Mindanda&amp;table=14</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ir Rigo (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Rigo&amp;table=14)</t>
+          <t>Invitation de Dieu Mindanda (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Dieu%20Mindanda&amp;table=14)</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Benie, Exau et Deo</t>
+          <t>Esthy Mayele</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Benie%2C%20Exau%20et%20Deo&amp;table=15</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Esthy%20Mayele&amp;table=14</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Benie, Exau et Deo (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Benie%2C%20Exau%20et%20Deo&amp;table=15)</t>
+          <t>Invitation de Esthy Mayele (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Esthy%20Mayele&amp;table=14)</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Elsa et Josepha</t>
+          <t>Ir Rigo</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Elsa%20et%20Josepha&amp;table=15</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Rigo&amp;table=14</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Elsa et Josepha (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Elsa%20et%20Josepha&amp;table=15)</t>
+          <t>Invitation de Ir Rigo (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Rigo&amp;table=14)</t>
         </is>
       </c>
     </row>
@@ -2978,17 +2978,17 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Qui et Grace</t>
+          <t>Benie, Exau et Deo</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Qui%20et%20Grace&amp;table=15</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Benie%2C%20Exau%20et%20Deo&amp;table=15</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Qui et Grace (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Qui%20et%20Grace&amp;table=15)</t>
+          <t>Invitation de Benie, Exau et Deo (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Benie%2C%20Exau%20et%20Deo&amp;table=15)</t>
         </is>
       </c>
     </row>
@@ -2998,17 +2998,17 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Elohime et Israëlla</t>
+          <t>Elsa et Josepha</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Elohime%20et%20Isra%C3%ABlla&amp;table=15</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Elsa%20et%20Josepha&amp;table=15</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Elohime et Israëlla (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Elohime%20et%20Isra%C3%ABlla&amp;table=15)</t>
+          <t>Invitation de Elsa et Josepha (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Elsa%20et%20Josepha&amp;table=15)</t>
         </is>
       </c>
     </row>
@@ -3018,17 +3018,17 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Deborah Malemba</t>
+          <t>Qui et Grace</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Deborah%20Malemba&amp;table=15</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Qui%20et%20Grace&amp;table=15</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Deborah Malemba (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Deborah%20Malemba&amp;table=15)</t>
+          <t>Invitation de Qui et Grace (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Qui%20et%20Grace&amp;table=15)</t>
         </is>
       </c>
     </row>
@@ -3038,57 +3038,57 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Oncle Zo couple</t>
+          <t>Elohime et Israëlla</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Oncle%20Zo%20couple&amp;table=15</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Elohime%20et%20Isra%C3%ABlla&amp;table=15</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Oncle Zo couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Oncle%20Zo%20couple&amp;table=15)</t>
+          <t>Invitation de Elohime et Israëlla (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Elohime%20et%20Isra%C3%ABlla&amp;table=15)</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Papa et Maman</t>
+          <t>Deborah Malemba</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Papa%20et%20Maman&amp;table=16</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Deborah%20Malemba&amp;table=15</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Papa et Maman (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Papa%20et%20Maman&amp;table=16)</t>
+          <t>Invitation de Deborah Malemba (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Deborah%20Malemba&amp;table=15)</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Miriam Kuse couple</t>
+          <t>Oncle Zo couple</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Miriam%20Kuse%20couple&amp;table=16</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Oncle%20Zo%20couple&amp;table=15</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Miriam Kuse couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Miriam%20Kuse%20couple&amp;table=16)</t>
+          <t>Invitation de Oncle Zo couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Oncle%20Zo%20couple&amp;table=15)</t>
         </is>
       </c>
     </row>
@@ -3098,17 +3098,17 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Tantine Vicky</t>
+          <t>Papa et Maman</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Tantine%20Vicky&amp;table=16</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Papa%20et%20Maman&amp;table=16</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Tantine Vicky (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Tantine%20Vicky&amp;table=16)</t>
+          <t>Invitation de Papa et Maman (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Papa%20et%20Maman&amp;table=16)</t>
         </is>
       </c>
     </row>
@@ -3118,17 +3118,17 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Gedeon Mutu</t>
+          <t>Miriam Kuse couple</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Gedeon%20Mutu&amp;table=16</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Miriam%20Kuse%20couple&amp;table=16</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Gedeon Mutu (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Gedeon%20Mutu&amp;table=16)</t>
+          <t>Invitation de Miriam Kuse couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Miriam%20Kuse%20couple&amp;table=16)</t>
         </is>
       </c>
     </row>
@@ -3138,17 +3138,17 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Mbangu Mutu</t>
+          <t>Tantine Vicky</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Mbangu%20Mutu&amp;table=16</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Tantine%20Vicky&amp;table=16</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Mbangu Mutu (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Mbangu%20Mutu&amp;table=16)</t>
+          <t>Invitation de Tantine Vicky (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Tantine%20Vicky&amp;table=16)</t>
         </is>
       </c>
     </row>
@@ -3158,17 +3158,17 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Juvenal Kuse</t>
+          <t>Gedeon Mutu</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Juvenal%20Kuse&amp;table=16</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Gedeon%20Mutu&amp;table=16</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Juvenal Kuse (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Juvenal%20Kuse&amp;table=16)</t>
+          <t>Invitation de Gedeon Mutu (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Gedeon%20Mutu&amp;table=16)</t>
         </is>
       </c>
     </row>
@@ -3178,17 +3178,17 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Ma Bienvenue couple</t>
+          <t>Mbangu Mutu</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ma%20Bienvenue%20couple&amp;table=16</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Mbangu%20Mutu&amp;table=16</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Ma Bienvenue couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ma%20Bienvenue%20couple&amp;table=16)</t>
+          <t>Invitation de Mbangu Mutu (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Mbangu%20Mutu&amp;table=16)</t>
         </is>
       </c>
     </row>
@@ -3198,17 +3198,17 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Mama</t>
+          <t>Juvenal Kuse</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Mama&amp;table=16</t>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Juvenal%20Kuse&amp;table=16</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Invitation de Mama (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Mama&amp;table=16)</t>
+          <t>Invitation de Juvenal Kuse (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Juvenal%20Kuse&amp;table=16)</t>
         </is>
       </c>
     </row>
@@ -3218,22 +3218,62 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
+          <t>Ma Bienvenue couple</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ma%20Bienvenue%20couple&amp;table=16</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Ma Bienvenue couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ma%20Bienvenue%20couple&amp;table=16)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Mama</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Mama&amp;table=16</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Invitation de Mama (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Mama&amp;table=16)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>Kulutu Kumbele</t>
         </is>
       </c>
-      <c r="C139" s="3" t="inlineStr">
+      <c r="C141" s="3" t="inlineStr">
         <is>
           <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Kulutu%20Kumbele&amp;table=16</t>
         </is>
       </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Invitation de Kulutu Kumbele (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Kulutu%20Kumbele&amp;table=16)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D139"/>
+  <autoFilter ref="A1:D141"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
@@ -3373,6 +3413,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C137" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C138" r:id="rId137"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C141" r:id="rId140"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/liste_invites.xlsx
+++ b/liste_invites.xlsx
@@ -453,15 +453,9 @@
     <t>Invitation de Prof Tshiula (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Prof%20Tshiula&amp;table=7)</t>
   </si>
   <si>
-    <t>Ir Fabrice couple</t>
-  </si>
-  <si>
     <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Fabrice%20couple&amp;table=7</t>
   </si>
   <si>
-    <t>Invitation de Ir Fabrice couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Fabrice%20couple&amp;table=7)</t>
-  </si>
-  <si>
     <t>Ir José</t>
   </si>
   <si>
@@ -471,15 +465,9 @@
     <t>Invitation de Ir José (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Jos%C3%A9&amp;table=7)</t>
   </si>
   <si>
-    <t>Ir Perci couple</t>
-  </si>
-  <si>
     <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Perci%20couple&amp;table=7</t>
   </si>
   <si>
-    <t>Invitation de Ir Perci couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Perci%20couple&amp;table=7)</t>
-  </si>
-  <si>
     <t>Archi Christian</t>
   </si>
   <si>
@@ -516,42 +504,18 @@
     <t>Invitation de Ingénieur BKA Ville (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ing%C3%A9nieur%20BKA%20Ville&amp;table=7)</t>
   </si>
   <si>
-    <t>Ir Johny couple</t>
-  </si>
-  <si>
     <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Johny%20couple&amp;table=8</t>
   </si>
   <si>
-    <t>Invitation de Ir Johny couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Johny%20couple&amp;table=8)</t>
-  </si>
-  <si>
-    <t>Ir Ridy couple</t>
-  </si>
-  <si>
     <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Ridy%20couple&amp;table=8</t>
   </si>
   <si>
-    <t>Invitation de Ir Ridy couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Ridy%20couple&amp;table=8)</t>
-  </si>
-  <si>
-    <t>Ir gentille couple</t>
-  </si>
-  <si>
     <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20gentille%20couple&amp;table=8</t>
   </si>
   <si>
-    <t>Invitation de Ir gentille couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20gentille%20couple&amp;table=8)</t>
-  </si>
-  <si>
-    <t>Ir Manase Bikila Or couple</t>
-  </si>
-  <si>
     <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Manase%20Bikila%20Or%20couple&amp;table=8</t>
   </si>
   <si>
-    <t>Invitation de Ir Manase Bikila Or couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Manase%20Bikila%20Or%20couple&amp;table=8)</t>
-  </si>
-  <si>
     <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Bricil%20Ntumba%20BKA%20couple&amp;table=8</t>
   </si>
   <si>
@@ -585,24 +549,12 @@
     <t>Invitation de Ir George (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20George&amp;table=8)</t>
   </si>
   <si>
-    <t>Ir Horizon couple</t>
-  </si>
-  <si>
     <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Horizon%20couple&amp;table=9</t>
   </si>
   <si>
-    <t>Invitation de Ir Horizon couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Horizon%20couple&amp;table=9)</t>
-  </si>
-  <si>
-    <t>Ir Juventus couple</t>
-  </si>
-  <si>
     <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Juventus%20couple&amp;table=9</t>
   </si>
   <si>
-    <t>Invitation de Ir Juventus couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Juventus%20couple&amp;table=9)</t>
-  </si>
-  <si>
     <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Jonathan%20Or%20couple&amp;table=9</t>
   </si>
   <si>
@@ -840,15 +792,9 @@
     <t>Invitation de Ir Bervely Totokani (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Bervely%20Totokani&amp;table=11)</t>
   </si>
   <si>
-    <t>Ir Palice Kumbelu couple</t>
-  </si>
-  <si>
     <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Palice%20Kumbelu%20couple&amp;table=11</t>
   </si>
   <si>
-    <t>Invitation de Ir Palice Kumbelu couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Palice%20Kumbelu%20couple&amp;table=11)</t>
-  </si>
-  <si>
     <t>Ir Péguy Mwana Mputu</t>
   </si>
   <si>
@@ -957,15 +903,9 @@
     <t>Invitation de Vx Junior (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Vx%20Junior&amp;table=13)</t>
   </si>
   <si>
-    <t>Mm Mitshia</t>
-  </si>
-  <si>
     <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Mm%20Mitshia&amp;table=13</t>
   </si>
   <si>
-    <t>Invitation de Mm Mitshia (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Mm%20Mitshia&amp;table=13)</t>
-  </si>
-  <si>
     <t>Couple Leon</t>
   </si>
   <si>
@@ -1173,9 +1113,6 @@
     <t>Invitation de Deborah Malemba (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Deborah%20Malemba&amp;table=15)</t>
   </si>
   <si>
-    <t>Oncle Zo couple</t>
-  </si>
-  <si>
     <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Oncle%20Zo%20couple&amp;table=15</t>
   </si>
   <si>
@@ -1191,15 +1128,9 @@
     <t>Invitation de Papa et Maman (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Papa%20et%20Maman&amp;table=16)</t>
   </si>
   <si>
-    <t>Miriam Kuse couple</t>
-  </si>
-  <si>
     <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Miriam%20Kuse%20couple&amp;table=16</t>
   </si>
   <si>
-    <t>Invitation de Miriam Kuse couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Miriam%20Kuse%20couple&amp;table=16)</t>
-  </si>
-  <si>
     <t>Tantine Vicky</t>
   </si>
   <si>
@@ -1236,15 +1167,9 @@
     <t>Invitation de Juvenal Kuse (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Juvenal%20Kuse&amp;table=16)</t>
   </si>
   <si>
-    <t>Ma Bienvenue couple</t>
-  </si>
-  <si>
     <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ma%20Bienvenue%20couple&amp;table=16</t>
   </si>
   <si>
-    <t>Invitation de Ma Bienvenue couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ma%20Bienvenue%20couple&amp;table=16)</t>
-  </si>
-  <si>
     <t>Mama</t>
   </si>
   <si>
@@ -1275,25 +1200,100 @@
     <t>Ir Naomie</t>
   </si>
   <si>
-    <t>Ir Judith couple</t>
-  </si>
-  <si>
     <t>Ir Grâce</t>
   </si>
   <si>
     <t>Invitation de Ir Grâce  (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Gr%C3%A2ce%20ACGT&amp;table=9)</t>
   </si>
   <si>
-    <t>Invitation de Ir Judith  couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Judith%20Acgt%20couple&amp;table=9)</t>
-  </si>
-  <si>
     <t>Invitation de Ir Naomie (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Naomie%20Acgt&amp;table=9)</t>
   </si>
   <si>
-    <t>Invitation de Ir Jonathan couple (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Jonathan%20Or%20couple&amp;table=9)</t>
-  </si>
-  <si>
-    <t>Ir Jonathan couple</t>
+    <t>Couple Ridy</t>
+  </si>
+  <si>
+    <t>Couple Fabrice</t>
+  </si>
+  <si>
+    <t>Invitation de Couple Fabrice (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Fabrice%20couple&amp;table=7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Couple Perci </t>
+  </si>
+  <si>
+    <t>Invitation de Couple Perci (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Perci%20couple&amp;table=7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Couple Johny </t>
+  </si>
+  <si>
+    <t>Invitation de Couple Johny (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Johny%20couple&amp;table=8)</t>
+  </si>
+  <si>
+    <t>Invitation de couple Ridy (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Ridy%20couple&amp;table=8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Couple Gentille </t>
+  </si>
+  <si>
+    <t>Invitation de couple gentille (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20gentille%20couple&amp;table=8)</t>
+  </si>
+  <si>
+    <t>Invitation de couple Manase Bikila (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Manase%20Bikila%20Or%20couple&amp;table=8)</t>
+  </si>
+  <si>
+    <t>couple Manase Bikila</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Couple Horizon </t>
+  </si>
+  <si>
+    <t>Invitation de Couple Horizon (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Horizon%20couple&amp;table=9)</t>
+  </si>
+  <si>
+    <t>Invitation de Couple Juventus (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Juventus%20couple&amp;table=9)</t>
+  </si>
+  <si>
+    <t>Invitation de Couple Jonathan (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Jonathan%20Or%20couple&amp;table=9)</t>
+  </si>
+  <si>
+    <t>Invitation de Couple Judith (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Judith%20Acgt%20couple&amp;table=9)</t>
+  </si>
+  <si>
+    <t>Couple Judith</t>
+  </si>
+  <si>
+    <t>Couple Jonathan</t>
+  </si>
+  <si>
+    <t>Couple Juventus</t>
+  </si>
+  <si>
+    <t>Couple Palice Kumbelu</t>
+  </si>
+  <si>
+    <t>Invitation de Couple Palice Kumbelu (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ir%20Palice%20Kumbelu%20couple&amp;table=11)</t>
+  </si>
+  <si>
+    <t>Mère Mitsha</t>
+  </si>
+  <si>
+    <t>Invitation de Mère Mitsha (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Mm%20Mitshia&amp;table=13)</t>
+  </si>
+  <si>
+    <t>Couple Miriam Kuse</t>
+  </si>
+  <si>
+    <t>Invitation de Couple Miriam Kuse (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Miriam%20Kuse%20couple&amp;table=16)</t>
+  </si>
+  <si>
+    <t>Couple Bienvenue</t>
+  </si>
+  <si>
+    <t>Invitation de Couple Bienvenue (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Ma%20Bienvenue%20couple&amp;table=16)</t>
+  </si>
+  <si>
+    <t>Couple Oncle Zo</t>
   </si>
 </sst>
 </file>
@@ -1664,8 +1664,8 @@
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="104.44140625" customWidth="1"/>
-    <col min="4" max="4" width="132.33203125" customWidth="1"/>
+    <col min="3" max="3" width="86.33203125" customWidth="1"/>
+    <col min="4" max="4" width="113.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -1693,7 +1693,7 @@
         <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>415</v>
+        <v>390</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -2009,7 +2009,7 @@
         <v>4</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>414</v>
+        <v>389</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>72</v>
@@ -2345,13 +2345,13 @@
         <v>7</v>
       </c>
       <c r="B49" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C49" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="D49" s="2" t="s">
-        <v>145</v>
+        <v>397</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
@@ -2359,13 +2359,13 @@
         <v>7</v>
       </c>
       <c r="B50" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
@@ -2373,13 +2373,13 @@
         <v>7</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>149</v>
+        <v>398</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>151</v>
+        <v>399</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
@@ -2387,13 +2387,13 @@
         <v>7</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
@@ -2401,13 +2401,13 @@
         <v>7</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
@@ -2415,13 +2415,13 @@
         <v>7</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
@@ -2429,13 +2429,13 @@
         <v>7</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
@@ -2443,13 +2443,13 @@
         <v>8</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>164</v>
+        <v>400</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>166</v>
+        <v>401</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
@@ -2457,13 +2457,13 @@
         <v>8</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>167</v>
+        <v>395</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>169</v>
+        <v>402</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
@@ -2471,13 +2471,13 @@
         <v>8</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>170</v>
+        <v>403</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>172</v>
+        <v>404</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
@@ -2485,13 +2485,13 @@
         <v>8</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>173</v>
+        <v>406</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>175</v>
+        <v>405</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
@@ -2499,13 +2499,13 @@
         <v>8</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>413</v>
+        <v>388</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
@@ -2513,13 +2513,13 @@
         <v>8</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
@@ -2527,13 +2527,13 @@
         <v>8</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
@@ -2541,13 +2541,13 @@
         <v>8</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
@@ -2555,13 +2555,13 @@
         <v>9</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>187</v>
+        <v>407</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>189</v>
+        <v>408</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
@@ -2569,13 +2569,13 @@
         <v>9</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>190</v>
+        <v>414</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>192</v>
+        <v>409</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
@@ -2583,13 +2583,13 @@
         <v>9</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
@@ -2597,13 +2597,13 @@
         <v>9</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
@@ -2611,13 +2611,13 @@
         <v>9</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>416</v>
+        <v>391</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>421</v>
+        <v>394</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
@@ -2625,13 +2625,13 @@
         <v>9</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>418</v>
+        <v>392</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>419</v>
+        <v>393</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
@@ -2639,13 +2639,13 @@
         <v>9</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
@@ -2653,13 +2653,13 @@
         <v>9</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
@@ -2667,13 +2667,13 @@
         <v>9</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
@@ -2681,13 +2681,13 @@
         <v>10</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
@@ -2695,13 +2695,13 @@
         <v>10</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
@@ -2709,13 +2709,13 @@
         <v>10</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
@@ -2723,13 +2723,13 @@
         <v>10</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
@@ -2737,13 +2737,13 @@
         <v>10</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
@@ -2751,13 +2751,13 @@
         <v>10</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
@@ -2765,13 +2765,13 @@
         <v>10</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
@@ -2779,13 +2779,13 @@
         <v>10</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
@@ -2793,13 +2793,13 @@
         <v>10</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
@@ -2807,13 +2807,13 @@
         <v>10</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
@@ -2821,13 +2821,13 @@
         <v>10</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
@@ -2835,13 +2835,13 @@
         <v>10</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
@@ -2849,13 +2849,13 @@
         <v>10</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>244</v>
+        <v>228</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
@@ -2863,13 +2863,13 @@
         <v>11</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
@@ -2877,13 +2877,13 @@
         <v>11</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
@@ -2891,13 +2891,13 @@
         <v>11</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
@@ -2905,13 +2905,13 @@
         <v>11</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
@@ -2919,13 +2919,13 @@
         <v>11</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
@@ -2933,13 +2933,13 @@
         <v>11</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>262</v>
+        <v>246</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
@@ -2947,13 +2947,13 @@
         <v>11</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>265</v>
+        <v>249</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
@@ -2961,13 +2961,13 @@
         <v>11</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>267</v>
+        <v>251</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>268</v>
+        <v>252</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
@@ -2975,13 +2975,13 @@
         <v>11</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>269</v>
+        <v>253</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>270</v>
+        <v>254</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>271</v>
+        <v>255</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
@@ -2989,13 +2989,13 @@
         <v>11</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>272</v>
+        <v>415</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>274</v>
+        <v>416</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
@@ -3003,13 +3003,13 @@
         <v>12</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>276</v>
+        <v>258</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
@@ -3017,13 +3017,13 @@
         <v>12</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>278</v>
+        <v>260</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>280</v>
+        <v>262</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
@@ -3031,13 +3031,13 @@
         <v>12</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
@@ -3045,13 +3045,13 @@
         <v>12</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>284</v>
+        <v>266</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>285</v>
+        <v>267</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
@@ -3059,13 +3059,13 @@
         <v>12</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
@@ -3073,13 +3073,13 @@
         <v>12</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>291</v>
+        <v>273</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>292</v>
+        <v>274</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
@@ -3087,13 +3087,13 @@
         <v>12</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>293</v>
+        <v>275</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>294</v>
+        <v>276</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
@@ -3101,13 +3101,13 @@
         <v>12</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>296</v>
+        <v>278</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>298</v>
+        <v>280</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
@@ -3115,13 +3115,13 @@
         <v>12</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>299</v>
+        <v>281</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
@@ -3129,13 +3129,13 @@
         <v>12</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>303</v>
+        <v>285</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
@@ -3143,13 +3143,13 @@
         <v>12</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>307</v>
+        <v>289</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
@@ -3157,13 +3157,13 @@
         <v>13</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>308</v>
+        <v>290</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>309</v>
+        <v>291</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>310</v>
+        <v>292</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
@@ -3171,13 +3171,13 @@
         <v>13</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>311</v>
+        <v>417</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>312</v>
+        <v>293</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>313</v>
+        <v>418</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
@@ -3185,13 +3185,13 @@
         <v>13</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>314</v>
+        <v>294</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>315</v>
+        <v>295</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>316</v>
+        <v>296</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
@@ -3199,13 +3199,13 @@
         <v>13</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>317</v>
+        <v>297</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>318</v>
+        <v>298</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>319</v>
+        <v>299</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
@@ -3213,13 +3213,13 @@
         <v>13</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>321</v>
+        <v>301</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>322</v>
+        <v>302</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
@@ -3227,13 +3227,13 @@
         <v>13</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>323</v>
+        <v>303</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>324</v>
+        <v>304</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
@@ -3241,13 +3241,13 @@
         <v>13</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>326</v>
+        <v>306</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>328</v>
+        <v>308</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
@@ -3255,13 +3255,13 @@
         <v>13</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>329</v>
+        <v>309</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>331</v>
+        <v>311</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
@@ -3269,13 +3269,13 @@
         <v>14</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>332</v>
+        <v>312</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>334</v>
+        <v>314</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
@@ -3283,13 +3283,13 @@
         <v>14</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>335</v>
+        <v>315</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>336</v>
+        <v>316</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>337</v>
+        <v>317</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
@@ -3297,13 +3297,13 @@
         <v>14</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>338</v>
+        <v>318</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>339</v>
+        <v>319</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
@@ -3311,13 +3311,13 @@
         <v>14</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>341</v>
+        <v>321</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>343</v>
+        <v>323</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
@@ -3325,13 +3325,13 @@
         <v>14</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>344</v>
+        <v>324</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>345</v>
+        <v>325</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>346</v>
+        <v>326</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
@@ -3339,13 +3339,13 @@
         <v>14</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>347</v>
+        <v>327</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>348</v>
+        <v>328</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>349</v>
+        <v>329</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
@@ -3353,13 +3353,13 @@
         <v>14</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>351</v>
+        <v>331</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>352</v>
+        <v>332</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
@@ -3367,13 +3367,13 @@
         <v>14</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>353</v>
+        <v>333</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>354</v>
+        <v>334</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>355</v>
+        <v>335</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
@@ -3381,13 +3381,13 @@
         <v>14</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>356</v>
+        <v>336</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>357</v>
+        <v>337</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>358</v>
+        <v>338</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
@@ -3395,13 +3395,13 @@
         <v>14</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>359</v>
+        <v>339</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>361</v>
+        <v>341</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
@@ -3409,13 +3409,13 @@
         <v>14</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>362</v>
+        <v>342</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>363</v>
+        <v>343</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>364</v>
+        <v>344</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
@@ -3423,13 +3423,13 @@
         <v>14</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>365</v>
+        <v>345</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>366</v>
+        <v>346</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
@@ -3437,13 +3437,13 @@
         <v>15</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>368</v>
+        <v>348</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>369</v>
+        <v>349</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>370</v>
+        <v>350</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
@@ -3451,13 +3451,13 @@
         <v>15</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>371</v>
+        <v>351</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>372</v>
+        <v>352</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>373</v>
+        <v>353</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
@@ -3465,13 +3465,13 @@
         <v>15</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>374</v>
+        <v>354</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>375</v>
+        <v>355</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>376</v>
+        <v>356</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
@@ -3479,13 +3479,13 @@
         <v>15</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>377</v>
+        <v>357</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>378</v>
+        <v>358</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>379</v>
+        <v>359</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
@@ -3493,13 +3493,13 @@
         <v>15</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>381</v>
+        <v>361</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>382</v>
+        <v>362</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
@@ -3507,13 +3507,13 @@
         <v>15</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>383</v>
+        <v>423</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>384</v>
+        <v>363</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>385</v>
+        <v>364</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
@@ -3521,13 +3521,13 @@
         <v>16</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>386</v>
+        <v>365</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>388</v>
+        <v>367</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
@@ -3535,13 +3535,13 @@
         <v>16</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>389</v>
+        <v>419</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>390</v>
+        <v>368</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>391</v>
+        <v>420</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
@@ -3549,13 +3549,13 @@
         <v>16</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>392</v>
+        <v>369</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>393</v>
+        <v>370</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>394</v>
+        <v>371</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
@@ -3563,13 +3563,13 @@
         <v>16</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>395</v>
+        <v>372</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>396</v>
+        <v>373</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>397</v>
+        <v>374</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.3">
@@ -3577,13 +3577,13 @@
         <v>16</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>399</v>
+        <v>376</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
@@ -3591,13 +3591,13 @@
         <v>16</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>402</v>
+        <v>379</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>403</v>
+        <v>380</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
@@ -3605,13 +3605,13 @@
         <v>16</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>404</v>
+        <v>421</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>405</v>
+        <v>381</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>406</v>
+        <v>422</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
@@ -3619,13 +3619,13 @@
         <v>16</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>407</v>
+        <v>382</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>408</v>
+        <v>383</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>409</v>
+        <v>384</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
@@ -3633,13 +3633,13 @@
         <v>16</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>410</v>
+        <v>385</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>411</v>
+        <v>386</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>412</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>

--- a/liste_invites.xlsx
+++ b/liste_invites.xlsx
@@ -243,9 +243,6 @@
     <t>https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Christian%20Kumatoka&amp;table=4</t>
   </si>
   <si>
-    <t>Invitation de Couple Christian Kumatoka (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Christian%20Kumatoka&amp;table=4)</t>
-  </si>
-  <si>
     <t>Couple Arma Ndongisila</t>
   </si>
   <si>
@@ -1294,6 +1291,9 @@
   </si>
   <si>
     <t>Couple Oncle Zo</t>
+  </si>
+  <si>
+    <t>Invitation de Christian Kumatoka (https://digiappkin.github.io/invitation-tresor-merveille/invitation.html?invite=Couple%20Christian%20Kumatoka&amp;table=4)</t>
   </si>
 </sst>
 </file>
@@ -1693,7 +1693,7 @@
         <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -2009,13 +2009,13 @@
         <v>4</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>72</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>73</v>
+        <v>423</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -2023,13 +2023,13 @@
         <v>4</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="D26" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -2037,13 +2037,13 @@
         <v>4</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="D27" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -2051,13 +2051,13 @@
         <v>4</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="D28" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -2065,13 +2065,13 @@
         <v>5</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="D29" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
@@ -2079,13 +2079,13 @@
         <v>5</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="D30" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
@@ -2093,13 +2093,13 @@
         <v>5</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="D31" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
@@ -2107,13 +2107,13 @@
         <v>5</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="D32" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -2121,13 +2121,13 @@
         <v>5</v>
       </c>
       <c r="B33" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="D33" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -2135,13 +2135,13 @@
         <v>5</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="D34" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
@@ -2149,13 +2149,13 @@
         <v>5</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="D35" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
@@ -2163,13 +2163,13 @@
         <v>5</v>
       </c>
       <c r="B36" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="D36" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
@@ -2177,13 +2177,13 @@
         <v>5</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="D37" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
@@ -2191,13 +2191,13 @@
         <v>5</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="D38" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
@@ -2205,13 +2205,13 @@
         <v>5</v>
       </c>
       <c r="B39" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="D39" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
@@ -2219,13 +2219,13 @@
         <v>6</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="D40" s="2" t="s">
         <v>117</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
@@ -2233,13 +2233,13 @@
         <v>6</v>
       </c>
       <c r="B41" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="D41" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
@@ -2247,13 +2247,13 @@
         <v>6</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="D42" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
@@ -2261,13 +2261,13 @@
         <v>6</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="D43" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
@@ -2275,13 +2275,13 @@
         <v>6</v>
       </c>
       <c r="B44" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="D44" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
@@ -2289,13 +2289,13 @@
         <v>6</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="D45" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
@@ -2303,13 +2303,13 @@
         <v>6</v>
       </c>
       <c r="B46" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="D46" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
@@ -2317,13 +2317,13 @@
         <v>7</v>
       </c>
       <c r="B47" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="D47" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
@@ -2331,13 +2331,13 @@
         <v>7</v>
       </c>
       <c r="B48" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="D48" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
@@ -2345,13 +2345,13 @@
         <v>7</v>
       </c>
       <c r="B49" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D49" s="2" t="s">
         <v>396</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
@@ -2359,13 +2359,13 @@
         <v>7</v>
       </c>
       <c r="B50" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="D50" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
@@ -2373,13 +2373,13 @@
         <v>7</v>
       </c>
       <c r="B51" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D51" s="2" t="s">
         <v>398</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
@@ -2387,13 +2387,13 @@
         <v>7</v>
       </c>
       <c r="B52" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="D52" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
@@ -2401,13 +2401,13 @@
         <v>7</v>
       </c>
       <c r="B53" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="D53" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
@@ -2415,13 +2415,13 @@
         <v>7</v>
       </c>
       <c r="B54" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C54" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="D54" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
@@ -2429,13 +2429,13 @@
         <v>7</v>
       </c>
       <c r="B55" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="D55" s="2" t="s">
         <v>158</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
@@ -2443,13 +2443,13 @@
         <v>8</v>
       </c>
       <c r="B56" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D56" s="2" t="s">
         <v>400</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
@@ -2457,13 +2457,13 @@
         <v>8</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
@@ -2471,13 +2471,13 @@
         <v>8</v>
       </c>
       <c r="B58" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D58" s="2" t="s">
         <v>403</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
@@ -2485,13 +2485,13 @@
         <v>8</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
@@ -2499,13 +2499,13 @@
         <v>8</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C60" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D60" s="2" t="s">
         <v>164</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
@@ -2513,13 +2513,13 @@
         <v>8</v>
       </c>
       <c r="B61" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C61" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="D61" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
@@ -2527,13 +2527,13 @@
         <v>8</v>
       </c>
       <c r="B62" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C62" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="D62" s="2" t="s">
         <v>170</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
@@ -2541,13 +2541,13 @@
         <v>8</v>
       </c>
       <c r="B63" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C63" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="D63" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
@@ -2555,13 +2555,13 @@
         <v>9</v>
       </c>
       <c r="B64" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D64" s="2" t="s">
         <v>407</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
@@ -2569,13 +2569,13 @@
         <v>9</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
@@ -2583,13 +2583,13 @@
         <v>9</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
@@ -2597,13 +2597,13 @@
         <v>9</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
@@ -2611,13 +2611,13 @@
         <v>9</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
@@ -2625,13 +2625,13 @@
         <v>9</v>
       </c>
       <c r="B69" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D69" s="2" t="s">
         <v>392</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
@@ -2639,13 +2639,13 @@
         <v>9</v>
       </c>
       <c r="B70" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C70" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="D70" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
@@ -2653,13 +2653,13 @@
         <v>9</v>
       </c>
       <c r="B71" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C71" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="D71" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
@@ -2667,13 +2667,13 @@
         <v>9</v>
       </c>
       <c r="B72" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C72" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="D72" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
@@ -2681,13 +2681,13 @@
         <v>10</v>
       </c>
       <c r="B73" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C73" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="D73" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
@@ -2695,13 +2695,13 @@
         <v>10</v>
       </c>
       <c r="B74" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C74" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="D74" s="2" t="s">
         <v>194</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
@@ -2709,13 +2709,13 @@
         <v>10</v>
       </c>
       <c r="B75" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C75" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="D75" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
@@ -2723,13 +2723,13 @@
         <v>10</v>
       </c>
       <c r="B76" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C76" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="D76" s="2" t="s">
         <v>200</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
@@ -2737,13 +2737,13 @@
         <v>10</v>
       </c>
       <c r="B77" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="C77" s="3" t="s">
+      <c r="D77" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
@@ -2751,13 +2751,13 @@
         <v>10</v>
       </c>
       <c r="B78" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C78" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="D78" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
@@ -2765,13 +2765,13 @@
         <v>10</v>
       </c>
       <c r="B79" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="D79" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
@@ -2779,13 +2779,13 @@
         <v>10</v>
       </c>
       <c r="B80" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C80" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="D80" s="2" t="s">
         <v>212</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
@@ -2793,13 +2793,13 @@
         <v>10</v>
       </c>
       <c r="B81" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C81" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="D81" s="2" t="s">
         <v>215</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
@@ -2807,13 +2807,13 @@
         <v>10</v>
       </c>
       <c r="B82" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C82" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="D82" s="2" t="s">
         <v>218</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
@@ -2821,13 +2821,13 @@
         <v>10</v>
       </c>
       <c r="B83" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C83" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="D83" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
@@ -2835,13 +2835,13 @@
         <v>10</v>
       </c>
       <c r="B84" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C84" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="C84" s="3" t="s">
+      <c r="D84" s="2" t="s">
         <v>224</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
@@ -2849,13 +2849,13 @@
         <v>10</v>
       </c>
       <c r="B85" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C85" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="D85" s="2" t="s">
         <v>227</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
@@ -2863,13 +2863,13 @@
         <v>11</v>
       </c>
       <c r="B86" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C86" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="C86" s="3" t="s">
+      <c r="D86" s="2" t="s">
         <v>230</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
@@ -2877,13 +2877,13 @@
         <v>11</v>
       </c>
       <c r="B87" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C87" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="D87" s="2" t="s">
         <v>233</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
@@ -2891,13 +2891,13 @@
         <v>11</v>
       </c>
       <c r="B88" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C88" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="C88" s="3" t="s">
+      <c r="D88" s="2" t="s">
         <v>236</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
@@ -2905,13 +2905,13 @@
         <v>11</v>
       </c>
       <c r="B89" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C89" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="C89" s="3" t="s">
+      <c r="D89" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
@@ -2919,13 +2919,13 @@
         <v>11</v>
       </c>
       <c r="B90" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C90" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="C90" s="3" t="s">
+      <c r="D90" s="2" t="s">
         <v>242</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
@@ -2933,13 +2933,13 @@
         <v>11</v>
       </c>
       <c r="B91" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C91" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="C91" s="3" t="s">
+      <c r="D91" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
@@ -2947,13 +2947,13 @@
         <v>11</v>
       </c>
       <c r="B92" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C92" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="C92" s="3" t="s">
+      <c r="D92" s="2" t="s">
         <v>248</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
@@ -2961,13 +2961,13 @@
         <v>11</v>
       </c>
       <c r="B93" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C93" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="C93" s="3" t="s">
+      <c r="D93" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
@@ -2975,13 +2975,13 @@
         <v>11</v>
       </c>
       <c r="B94" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C94" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="C94" s="3" t="s">
+      <c r="D94" s="2" t="s">
         <v>254</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
@@ -2989,13 +2989,13 @@
         <v>11</v>
       </c>
       <c r="B95" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="D95" s="2" t="s">
         <v>415</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
@@ -3003,13 +3003,13 @@
         <v>12</v>
       </c>
       <c r="B96" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C96" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="C96" s="3" t="s">
+      <c r="D96" s="2" t="s">
         <v>258</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
@@ -3017,13 +3017,13 @@
         <v>12</v>
       </c>
       <c r="B97" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C97" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="C97" s="3" t="s">
+      <c r="D97" s="2" t="s">
         <v>261</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
@@ -3031,13 +3031,13 @@
         <v>12</v>
       </c>
       <c r="B98" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C98" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="C98" s="3" t="s">
+      <c r="D98" s="2" t="s">
         <v>264</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
@@ -3045,13 +3045,13 @@
         <v>12</v>
       </c>
       <c r="B99" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C99" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="C99" s="3" t="s">
+      <c r="D99" s="2" t="s">
         <v>267</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
@@ -3059,13 +3059,13 @@
         <v>12</v>
       </c>
       <c r="B100" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C100" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="C100" s="3" t="s">
+      <c r="D100" s="2" t="s">
         <v>270</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
@@ -3073,13 +3073,13 @@
         <v>12</v>
       </c>
       <c r="B101" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C101" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="C101" s="3" t="s">
+      <c r="D101" s="2" t="s">
         <v>273</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
@@ -3087,13 +3087,13 @@
         <v>12</v>
       </c>
       <c r="B102" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C102" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="C102" s="3" t="s">
+      <c r="D102" s="2" t="s">
         <v>276</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
@@ -3101,13 +3101,13 @@
         <v>12</v>
       </c>
       <c r="B103" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C103" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="C103" s="3" t="s">
+      <c r="D103" s="2" t="s">
         <v>279</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
@@ -3115,13 +3115,13 @@
         <v>12</v>
       </c>
       <c r="B104" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C104" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="C104" s="3" t="s">
+      <c r="D104" s="2" t="s">
         <v>282</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
@@ -3129,13 +3129,13 @@
         <v>12</v>
       </c>
       <c r="B105" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C105" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="C105" s="3" t="s">
+      <c r="D105" s="2" t="s">
         <v>285</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
@@ -3143,13 +3143,13 @@
         <v>12</v>
       </c>
       <c r="B106" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C106" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="C106" s="3" t="s">
+      <c r="D106" s="2" t="s">
         <v>288</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
@@ -3157,13 +3157,13 @@
         <v>13</v>
       </c>
       <c r="B107" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C107" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="C107" s="3" t="s">
+      <c r="D107" s="2" t="s">
         <v>291</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
@@ -3171,13 +3171,13 @@
         <v>13</v>
       </c>
       <c r="B108" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="D108" s="2" t="s">
         <v>417</v>
-      </c>
-      <c r="C108" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
@@ -3185,13 +3185,13 @@
         <v>13</v>
       </c>
       <c r="B109" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C109" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="C109" s="3" t="s">
+      <c r="D109" s="2" t="s">
         <v>295</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
@@ -3199,13 +3199,13 @@
         <v>13</v>
       </c>
       <c r="B110" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C110" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="C110" s="3" t="s">
+      <c r="D110" s="2" t="s">
         <v>298</v>
-      </c>
-      <c r="D110" s="2" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
@@ -3213,13 +3213,13 @@
         <v>13</v>
       </c>
       <c r="B111" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C111" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="C111" s="3" t="s">
+      <c r="D111" s="2" t="s">
         <v>301</v>
-      </c>
-      <c r="D111" s="2" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
@@ -3227,13 +3227,13 @@
         <v>13</v>
       </c>
       <c r="B112" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C112" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="C112" s="3" t="s">
+      <c r="D112" s="2" t="s">
         <v>304</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
@@ -3241,13 +3241,13 @@
         <v>13</v>
       </c>
       <c r="B113" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C113" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="C113" s="3" t="s">
+      <c r="D113" s="2" t="s">
         <v>307</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
@@ -3255,13 +3255,13 @@
         <v>13</v>
       </c>
       <c r="B114" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C114" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="C114" s="3" t="s">
+      <c r="D114" s="2" t="s">
         <v>310</v>
-      </c>
-      <c r="D114" s="2" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
@@ -3269,13 +3269,13 @@
         <v>14</v>
       </c>
       <c r="B115" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C115" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="C115" s="3" t="s">
+      <c r="D115" s="2" t="s">
         <v>313</v>
-      </c>
-      <c r="D115" s="2" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
@@ -3283,13 +3283,13 @@
         <v>14</v>
       </c>
       <c r="B116" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C116" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="C116" s="3" t="s">
+      <c r="D116" s="2" t="s">
         <v>316</v>
-      </c>
-      <c r="D116" s="2" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
@@ -3297,13 +3297,13 @@
         <v>14</v>
       </c>
       <c r="B117" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C117" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="C117" s="3" t="s">
+      <c r="D117" s="2" t="s">
         <v>319</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
@@ -3311,13 +3311,13 @@
         <v>14</v>
       </c>
       <c r="B118" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="C118" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="C118" s="3" t="s">
+      <c r="D118" s="2" t="s">
         <v>322</v>
-      </c>
-      <c r="D118" s="2" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
@@ -3325,13 +3325,13 @@
         <v>14</v>
       </c>
       <c r="B119" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C119" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="C119" s="3" t="s">
+      <c r="D119" s="2" t="s">
         <v>325</v>
-      </c>
-      <c r="D119" s="2" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
@@ -3339,13 +3339,13 @@
         <v>14</v>
       </c>
       <c r="B120" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C120" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="C120" s="3" t="s">
+      <c r="D120" s="2" t="s">
         <v>328</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
@@ -3353,13 +3353,13 @@
         <v>14</v>
       </c>
       <c r="B121" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C121" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="C121" s="3" t="s">
+      <c r="D121" s="2" t="s">
         <v>331</v>
-      </c>
-      <c r="D121" s="2" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
@@ -3367,13 +3367,13 @@
         <v>14</v>
       </c>
       <c r="B122" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="C122" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="C122" s="3" t="s">
+      <c r="D122" s="2" t="s">
         <v>334</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
@@ -3381,13 +3381,13 @@
         <v>14</v>
       </c>
       <c r="B123" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C123" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="C123" s="3" t="s">
+      <c r="D123" s="2" t="s">
         <v>337</v>
-      </c>
-      <c r="D123" s="2" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
@@ -3395,13 +3395,13 @@
         <v>14</v>
       </c>
       <c r="B124" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C124" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="C124" s="3" t="s">
+      <c r="D124" s="2" t="s">
         <v>340</v>
-      </c>
-      <c r="D124" s="2" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
@@ -3409,13 +3409,13 @@
         <v>14</v>
       </c>
       <c r="B125" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C125" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="C125" s="3" t="s">
+      <c r="D125" s="2" t="s">
         <v>343</v>
-      </c>
-      <c r="D125" s="2" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
@@ -3423,13 +3423,13 @@
         <v>14</v>
       </c>
       <c r="B126" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C126" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="C126" s="3" t="s">
+      <c r="D126" s="2" t="s">
         <v>346</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
@@ -3437,13 +3437,13 @@
         <v>15</v>
       </c>
       <c r="B127" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="C127" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="C127" s="3" t="s">
+      <c r="D127" s="2" t="s">
         <v>349</v>
-      </c>
-      <c r="D127" s="2" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
@@ -3451,13 +3451,13 @@
         <v>15</v>
       </c>
       <c r="B128" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C128" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="C128" s="3" t="s">
+      <c r="D128" s="2" t="s">
         <v>352</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
@@ -3465,13 +3465,13 @@
         <v>15</v>
       </c>
       <c r="B129" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="C129" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="C129" s="3" t="s">
+      <c r="D129" s="2" t="s">
         <v>355</v>
-      </c>
-      <c r="D129" s="2" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
@@ -3479,13 +3479,13 @@
         <v>15</v>
       </c>
       <c r="B130" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="C130" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="C130" s="3" t="s">
+      <c r="D130" s="2" t="s">
         <v>358</v>
-      </c>
-      <c r="D130" s="2" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
@@ -3493,13 +3493,13 @@
         <v>15</v>
       </c>
       <c r="B131" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C131" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="C131" s="3" t="s">
+      <c r="D131" s="2" t="s">
         <v>361</v>
-      </c>
-      <c r="D131" s="2" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
@@ -3507,13 +3507,13 @@
         <v>15</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C132" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="D132" s="2" t="s">
         <v>363</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
@@ -3521,13 +3521,13 @@
         <v>16</v>
       </c>
       <c r="B133" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="C133" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="C133" s="3" t="s">
+      <c r="D133" s="2" t="s">
         <v>366</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
@@ -3535,13 +3535,13 @@
         <v>16</v>
       </c>
       <c r="B134" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="D134" s="2" t="s">
         <v>419</v>
-      </c>
-      <c r="C134" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="D134" s="2" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
@@ -3549,13 +3549,13 @@
         <v>16</v>
       </c>
       <c r="B135" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C135" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="C135" s="3" t="s">
+      <c r="D135" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="D135" s="2" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
@@ -3563,13 +3563,13 @@
         <v>16</v>
       </c>
       <c r="B136" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C136" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="C136" s="3" t="s">
+      <c r="D136" s="2" t="s">
         <v>373</v>
-      </c>
-      <c r="D136" s="2" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.3">
@@ -3577,13 +3577,13 @@
         <v>16</v>
       </c>
       <c r="B137" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="C137" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="C137" s="3" t="s">
+      <c r="D137" s="2" t="s">
         <v>376</v>
-      </c>
-      <c r="D137" s="2" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
@@ -3591,13 +3591,13 @@
         <v>16</v>
       </c>
       <c r="B138" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="C138" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="C138" s="3" t="s">
+      <c r="D138" s="2" t="s">
         <v>379</v>
-      </c>
-      <c r="D138" s="2" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
@@ -3605,13 +3605,13 @@
         <v>16</v>
       </c>
       <c r="B139" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="D139" s="2" t="s">
         <v>421</v>
-      </c>
-      <c r="C139" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="D139" s="2" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
@@ -3619,13 +3619,13 @@
         <v>16</v>
       </c>
       <c r="B140" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="C140" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="C140" s="3" t="s">
+      <c r="D140" s="2" t="s">
         <v>383</v>
-      </c>
-      <c r="D140" s="2" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
@@ -3633,13 +3633,13 @@
         <v>16</v>
       </c>
       <c r="B141" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C141" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="C141" s="3" t="s">
+      <c r="D141" s="2" t="s">
         <v>386</v>
-      </c>
-      <c r="D141" s="2" t="s">
-        <v>387</v>
       </c>
     </row>
   </sheetData>
